--- a/research/traditional_assets/database/data/singapore/singapore_trucking.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_trucking.xlsx
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1528,22 +1528,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08164401643118134</v>
+        <v>0.08154257160324833</v>
       </c>
       <c r="C2">
-        <v>24.56575641109163</v>
+        <v>24.32036704768178</v>
       </c>
       <c r="D2">
-        <v>1.965756411091625</v>
+        <v>1.96606704768178</v>
       </c>
       <c r="E2">
-        <v>-8.67</v>
+        <v>-8.424300000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2457</v>
       </c>
       <c r="G2">
         <v>22.6</v>
@@ -1564,28 +1564,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01235871</v>
       </c>
       <c r="N2">
-        <v>2.750204081632654</v>
+        <v>2.737845371632654</v>
       </c>
       <c r="O2">
-        <v>0.4675346938775511</v>
+        <v>0.4654337131775512</v>
       </c>
       <c r="P2">
-        <v>2.282669387755103</v>
+        <v>2.272411658455102</v>
       </c>
       <c r="Q2">
-        <v>10.0426693877551</v>
+        <v>10.0324116584551</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08164401643118134</v>
+        <v>0.08194452687196802</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919478</v>
+        <v>0.8347465790292844</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>222.5316462343282</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08154257160324833</v>
+        <v>0.08144112677531533</v>
       </c>
       <c r="C3">
-        <v>24.32036704768178</v>
+        <v>24.0749777824635</v>
       </c>
       <c r="D3">
-        <v>1.96606704768178</v>
+        <v>1.966377782463493</v>
       </c>
       <c r="E3">
-        <v>-8.424300000000001</v>
+        <v>-8.178599999999999</v>
       </c>
       <c r="F3">
-        <v>0.2457</v>
+        <v>0.4914</v>
       </c>
       <c r="G3">
         <v>22.6</v>
@@ -1646,28 +1646,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M3">
-        <v>0.01235871</v>
+        <v>0.02471742</v>
       </c>
       <c r="N3">
-        <v>2.737845371632654</v>
+        <v>2.725486661632654</v>
       </c>
       <c r="O3">
-        <v>0.4654337131775512</v>
+        <v>0.4633327324775511</v>
       </c>
       <c r="P3">
-        <v>2.272411658455102</v>
+        <v>2.262153929155103</v>
       </c>
       <c r="Q3">
-        <v>10.0324116584551</v>
+        <v>10.0221539291551</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08194452687196802</v>
+        <v>0.08225117017889319</v>
       </c>
       <c r="T3">
-        <v>0.8347465790292844</v>
+        <v>0.8418284105979952</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>222.5316462343282</v>
+        <v>111.2658231171641</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08144112677531533</v>
+        <v>0.08133968194738231</v>
       </c>
       <c r="C4">
-        <v>24.0749777824635</v>
+        <v>23.82958861548333</v>
       </c>
       <c r="D4">
-        <v>1.966377782463493</v>
+        <v>1.966688615483328</v>
       </c>
       <c r="E4">
-        <v>-8.178599999999999</v>
+        <v>-7.9329</v>
       </c>
       <c r="F4">
-        <v>0.4914</v>
+        <v>0.7371</v>
       </c>
       <c r="G4">
         <v>22.6</v>
@@ -1728,28 +1728,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M4">
-        <v>0.02471742</v>
+        <v>0.03707613</v>
       </c>
       <c r="N4">
-        <v>2.725486661632654</v>
+        <v>2.713127951632654</v>
       </c>
       <c r="O4">
-        <v>0.4633327324775511</v>
+        <v>0.4612317517775512</v>
       </c>
       <c r="P4">
-        <v>2.262153929155103</v>
+        <v>2.251896199855103</v>
       </c>
       <c r="Q4">
-        <v>10.0221539291551</v>
+        <v>10.0118961998551</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08225117017889319</v>
+        <v>0.08256413602822918</v>
       </c>
       <c r="T4">
-        <v>0.8418284105979952</v>
+        <v>0.8490562593124524</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>111.2658231171641</v>
+        <v>74.17721541144272</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08133968194738231</v>
+        <v>0.0812382371194493</v>
       </c>
       <c r="C5">
-        <v>23.82958861548333</v>
+        <v>23.58419954678788</v>
       </c>
       <c r="D5">
-        <v>1.966688615483328</v>
+        <v>1.96699954678788</v>
       </c>
       <c r="E5">
-        <v>-7.9329</v>
+        <v>-7.6872</v>
       </c>
       <c r="F5">
-        <v>0.7371</v>
+        <v>0.9828</v>
       </c>
       <c r="G5">
         <v>22.6</v>
@@ -1810,28 +1810,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M5">
-        <v>0.03707613</v>
+        <v>0.04943484</v>
       </c>
       <c r="N5">
-        <v>2.713127951632654</v>
+        <v>2.700769241632654</v>
       </c>
       <c r="O5">
-        <v>0.4612317517775512</v>
+        <v>0.4591307710775511</v>
       </c>
       <c r="P5">
-        <v>2.251896199855103</v>
+        <v>2.241638470555102</v>
       </c>
       <c r="Q5">
-        <v>10.0118961998551</v>
+        <v>10.0016384705551</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08256413602822918</v>
+        <v>0.08288362199942637</v>
       </c>
       <c r="T5">
-        <v>0.8490562593124524</v>
+        <v>0.8564346882084611</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>74.17721541144272</v>
+        <v>55.63291155858204</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0812382371194493</v>
+        <v>0.08113679229151631</v>
       </c>
       <c r="C6">
-        <v>23.58419954678788</v>
+        <v>23.33881057642377</v>
       </c>
       <c r="D6">
-        <v>1.96699954678788</v>
+        <v>1.967310576423771</v>
       </c>
       <c r="E6">
-        <v>-7.6872</v>
+        <v>-7.4415</v>
       </c>
       <c r="F6">
-        <v>0.9828</v>
+        <v>1.2285</v>
       </c>
       <c r="G6">
         <v>22.6</v>
@@ -1892,28 +1892,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M6">
-        <v>0.04943484</v>
+        <v>0.06179355</v>
       </c>
       <c r="N6">
-        <v>2.700769241632654</v>
+        <v>2.688410531632654</v>
       </c>
       <c r="O6">
-        <v>0.4591307710775511</v>
+        <v>0.4570297903775511</v>
       </c>
       <c r="P6">
-        <v>2.241638470555102</v>
+        <v>2.231380741255102</v>
       </c>
       <c r="Q6">
-        <v>10.0016384705551</v>
+        <v>9.991380741255103</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08288362199942637</v>
+        <v>0.08320983399106979</v>
       </c>
       <c r="T6">
-        <v>0.8564346882084611</v>
+        <v>0.8639684524496487</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.63291155858204</v>
+        <v>44.50632924686563</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08113679229151631</v>
+        <v>0.08103534746358329</v>
       </c>
       <c r="C7">
-        <v>23.33881057642377</v>
+        <v>23.09342170443766</v>
       </c>
       <c r="D7">
-        <v>1.967310576423771</v>
+        <v>1.967621704437656</v>
       </c>
       <c r="E7">
-        <v>-7.4415</v>
+        <v>-7.1958</v>
       </c>
       <c r="F7">
-        <v>1.2285</v>
+        <v>1.4742</v>
       </c>
       <c r="G7">
         <v>22.6</v>
@@ -1974,28 +1974,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M7">
-        <v>0.06179355</v>
+        <v>0.07415226000000001</v>
       </c>
       <c r="N7">
-        <v>2.688410531632654</v>
+        <v>2.676051821632654</v>
       </c>
       <c r="O7">
-        <v>0.4570297903775511</v>
+        <v>0.4549288096775512</v>
       </c>
       <c r="P7">
-        <v>2.231380741255102</v>
+        <v>2.221123011955103</v>
       </c>
       <c r="Q7">
-        <v>9.991380741255103</v>
+        <v>9.981123011955104</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08320983399106979</v>
+        <v>0.08354298666338648</v>
       </c>
       <c r="T7">
-        <v>0.8639684524496487</v>
+        <v>0.8716625095470319</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.50632924686563</v>
+        <v>37.08860770572135</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08103534746358329</v>
+        <v>0.08093390263565028</v>
       </c>
       <c r="C8">
-        <v>23.09342170443766</v>
+        <v>22.84803293087622</v>
       </c>
       <c r="D8">
-        <v>1.967621704437656</v>
+        <v>1.967932930876215</v>
       </c>
       <c r="E8">
-        <v>-7.1958</v>
+        <v>-6.9501</v>
       </c>
       <c r="F8">
-        <v>1.4742</v>
+        <v>1.7199</v>
       </c>
       <c r="G8">
         <v>22.6</v>
@@ -2056,28 +2056,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M8">
-        <v>0.07415226</v>
+        <v>0.08651096999999998</v>
       </c>
       <c r="N8">
-        <v>2.676051821632654</v>
+        <v>2.663693111632654</v>
       </c>
       <c r="O8">
-        <v>0.4549288096775512</v>
+        <v>0.4528278289775511</v>
       </c>
       <c r="P8">
-        <v>2.221123011955103</v>
+        <v>2.210865282655103</v>
       </c>
       <c r="Q8">
-        <v>9.981123011955104</v>
+        <v>9.970865282655103</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08354298666338648</v>
+        <v>0.08388330390930138</v>
       </c>
       <c r="T8">
-        <v>0.8716625095470319</v>
+        <v>0.8795220302379072</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.08860770572136</v>
+        <v>31.7902351763326</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08093390263565028</v>
+        <v>0.08083245780771728</v>
       </c>
       <c r="C9">
-        <v>22.84803293087622</v>
+        <v>22.60264425578616</v>
       </c>
       <c r="D9">
-        <v>1.967932930876215</v>
+        <v>1.968244255786162</v>
       </c>
       <c r="E9">
-        <v>-6.9501</v>
+        <v>-6.7044</v>
       </c>
       <c r="F9">
-        <v>1.7199</v>
+        <v>1.9656</v>
       </c>
       <c r="G9">
         <v>22.6</v>
@@ -2138,28 +2138,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M9">
-        <v>0.08651097000000001</v>
+        <v>0.09886968</v>
       </c>
       <c r="N9">
-        <v>2.663693111632654</v>
+        <v>2.651334401632654</v>
       </c>
       <c r="O9">
-        <v>0.4528278289775511</v>
+        <v>0.4507268482775512</v>
       </c>
       <c r="P9">
-        <v>2.210865282655103</v>
+        <v>2.200607553355102</v>
       </c>
       <c r="Q9">
-        <v>9.970865282655103</v>
+        <v>9.960607553355104</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08388330390930138</v>
+        <v>0.08423101935621444</v>
       </c>
       <c r="T9">
-        <v>0.8795220302379072</v>
+        <v>0.8875524100742362</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.79023517633259</v>
+        <v>27.81645577929102</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08083245780771728</v>
+        <v>0.08073101297978427</v>
       </c>
       <c r="C10">
-        <v>22.60264425578616</v>
+        <v>22.35725567921424</v>
       </c>
       <c r="D10">
-        <v>1.968244255786162</v>
+        <v>1.968555679214238</v>
       </c>
       <c r="E10">
-        <v>-6.7044</v>
+        <v>-6.4587</v>
       </c>
       <c r="F10">
-        <v>1.9656</v>
+        <v>2.2113</v>
       </c>
       <c r="G10">
         <v>22.6</v>
@@ -2220,28 +2220,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M10">
-        <v>0.09886968</v>
+        <v>0.11122839</v>
       </c>
       <c r="N10">
-        <v>2.651334401632654</v>
+        <v>2.638975691632654</v>
       </c>
       <c r="O10">
-        <v>0.4507268482775512</v>
+        <v>0.4486258675775511</v>
       </c>
       <c r="P10">
-        <v>2.200607553355102</v>
+        <v>2.190349824055103</v>
       </c>
       <c r="Q10">
-        <v>9.960607553355104</v>
+        <v>9.950349824055102</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08423101935621444</v>
+        <v>0.08458637690086183</v>
       </c>
       <c r="T10">
-        <v>0.8875524100742362</v>
+        <v>0.8957592817751001</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.81645577929102</v>
+        <v>24.72573847048091</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08073101297978427</v>
+        <v>0.08062956815185127</v>
       </c>
       <c r="C11">
-        <v>22.35725567921424</v>
+        <v>22.11186720120721</v>
       </c>
       <c r="D11">
-        <v>1.968555679214238</v>
+        <v>1.968867201207214</v>
       </c>
       <c r="E11">
-        <v>-6.4587</v>
+        <v>-6.213</v>
       </c>
       <c r="F11">
-        <v>2.2113</v>
+        <v>2.457</v>
       </c>
       <c r="G11">
         <v>22.6</v>
@@ -2302,28 +2302,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M11">
-        <v>0.11122839</v>
+        <v>0.1235871</v>
       </c>
       <c r="N11">
-        <v>2.638975691632654</v>
+        <v>2.626616981632654</v>
       </c>
       <c r="O11">
-        <v>0.4486258675775511</v>
+        <v>0.4465248868775512</v>
       </c>
       <c r="P11">
-        <v>2.190349824055103</v>
+        <v>2.180092094755103</v>
       </c>
       <c r="Q11">
-        <v>9.950349824055102</v>
+        <v>9.940092094755103</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08458637690086183</v>
+        <v>0.08494963127983474</v>
       </c>
       <c r="T11">
-        <v>0.8957592817751001</v>
+        <v>0.9041485284026497</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.72573847048091</v>
+        <v>22.25316462343282</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08062956815185127</v>
+        <v>0.08052812332391825</v>
       </c>
       <c r="C12">
-        <v>22.11186720120721</v>
+        <v>21.86647882181189</v>
       </c>
       <c r="D12">
-        <v>1.968867201207214</v>
+        <v>1.969178821811891</v>
       </c>
       <c r="E12">
-        <v>-6.212999999999999</v>
+        <v>-5.9673</v>
       </c>
       <c r="F12">
-        <v>2.457</v>
+        <v>2.7027</v>
       </c>
       <c r="G12">
         <v>22.6</v>
@@ -2384,28 +2384,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M12">
-        <v>0.1235871</v>
+        <v>0.13594581</v>
       </c>
       <c r="N12">
-        <v>2.626616981632654</v>
+        <v>2.614258271632654</v>
       </c>
       <c r="O12">
-        <v>0.4465248868775512</v>
+        <v>0.4444239061775512</v>
       </c>
       <c r="P12">
-        <v>2.180092094755103</v>
+        <v>2.169834365455102</v>
       </c>
       <c r="Q12">
-        <v>9.940092094755103</v>
+        <v>9.929834365455104</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08494963127983474</v>
+        <v>0.08532104867855983</v>
       </c>
       <c r="T12">
-        <v>0.9041485284026497</v>
+        <v>0.9127262974263241</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.25316462343281</v>
+        <v>20.2301496576662</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08052812332391825</v>
+        <v>0.08042667849598524</v>
       </c>
       <c r="C13">
-        <v>21.86647882181189</v>
+        <v>21.6210905410751</v>
       </c>
       <c r="D13">
-        <v>1.969178821811891</v>
+        <v>1.9694905410751</v>
       </c>
       <c r="E13">
-        <v>-5.9673</v>
+        <v>-5.7216</v>
       </c>
       <c r="F13">
-        <v>2.7027</v>
+        <v>2.9484</v>
       </c>
       <c r="G13">
         <v>22.6</v>
@@ -2466,28 +2466,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M13">
-        <v>0.13594581</v>
+        <v>0.14830452</v>
       </c>
       <c r="N13">
-        <v>2.614258271632654</v>
+        <v>2.601899561632654</v>
       </c>
       <c r="O13">
-        <v>0.4444239061775512</v>
+        <v>0.4423229254775511</v>
       </c>
       <c r="P13">
-        <v>2.169834365455102</v>
+        <v>2.159576636155102</v>
       </c>
       <c r="Q13">
-        <v>9.929834365455104</v>
+        <v>9.919576636155103</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08532104867855983</v>
+        <v>0.08570090738180142</v>
       </c>
       <c r="T13">
-        <v>0.9127262974263241</v>
+        <v>0.9214990157459911</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.2301496576662</v>
+        <v>18.54430385286068</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08042667849598524</v>
+        <v>0.08032523366805223</v>
       </c>
       <c r="C14">
-        <v>21.6210905410751</v>
+        <v>21.3757023590437</v>
       </c>
       <c r="D14">
-        <v>1.9694905410751</v>
+        <v>1.969802359043699</v>
       </c>
       <c r="E14">
-        <v>-5.7216</v>
+        <v>-5.475899999999999</v>
       </c>
       <c r="F14">
-        <v>2.9484</v>
+        <v>3.1941</v>
       </c>
       <c r="G14">
         <v>22.6</v>
@@ -2548,28 +2548,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M14">
-        <v>0.14830452</v>
+        <v>0.16066323</v>
       </c>
       <c r="N14">
-        <v>2.601899561632654</v>
+        <v>2.589540851632654</v>
       </c>
       <c r="O14">
-        <v>0.4423229254775511</v>
+        <v>0.4402219447775512</v>
       </c>
       <c r="P14">
-        <v>2.159576636155102</v>
+        <v>2.149318906855103</v>
       </c>
       <c r="Q14">
-        <v>9.919576636155103</v>
+        <v>9.909318906855104</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08570090738180142</v>
+        <v>0.08608949846902555</v>
       </c>
       <c r="T14">
-        <v>0.9214990157459911</v>
+        <v>0.9304734057511675</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.54430385286068</v>
+        <v>17.11781894110216</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08032523366805223</v>
+        <v>0.08022378884011921</v>
       </c>
       <c r="C15">
-        <v>21.3757023590437</v>
+        <v>21.13031427576458</v>
       </c>
       <c r="D15">
-        <v>1.969802359043699</v>
+        <v>1.970114275764581</v>
       </c>
       <c r="E15">
-        <v>-5.475899999999999</v>
+        <v>-5.2302</v>
       </c>
       <c r="F15">
-        <v>3.1941</v>
+        <v>3.4398</v>
       </c>
       <c r="G15">
         <v>22.6</v>
@@ -2630,28 +2630,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M15">
-        <v>0.16066323</v>
+        <v>0.17302194</v>
       </c>
       <c r="N15">
-        <v>2.589540851632654</v>
+        <v>2.577182141632654</v>
       </c>
       <c r="O15">
-        <v>0.4402219447775512</v>
+        <v>0.4381209640775511</v>
       </c>
       <c r="P15">
-        <v>2.149318906855103</v>
+        <v>2.139061177555102</v>
       </c>
       <c r="Q15">
-        <v>9.909318906855104</v>
+        <v>9.899061177555103</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08608949846902555</v>
+        <v>0.08648712655827817</v>
       </c>
       <c r="T15">
-        <v>0.9304734057511675</v>
+        <v>0.9396565025006507</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.11781894110216</v>
+        <v>15.8951175881663</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08022378884011921</v>
+        <v>0.08012234401218621</v>
       </c>
       <c r="C16">
-        <v>21.13031427576458</v>
+        <v>20.88492629128466</v>
       </c>
       <c r="D16">
-        <v>1.970114275764581</v>
+        <v>1.970426291284663</v>
       </c>
       <c r="E16">
-        <v>-5.2302</v>
+        <v>-4.984499999999999</v>
       </c>
       <c r="F16">
-        <v>3.4398</v>
+        <v>3.685500000000001</v>
       </c>
       <c r="G16">
         <v>22.6</v>
@@ -2712,28 +2712,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M16">
-        <v>0.17302194</v>
+        <v>0.18538065</v>
       </c>
       <c r="N16">
-        <v>2.577182141632654</v>
+        <v>2.564823431632654</v>
       </c>
       <c r="O16">
-        <v>0.4381209640775511</v>
+        <v>0.4360199833775512</v>
       </c>
       <c r="P16">
-        <v>2.139061177555102</v>
+        <v>2.128803448255102</v>
       </c>
       <c r="Q16">
-        <v>9.899061177555103</v>
+        <v>9.888803448255103</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08648712655827817</v>
+        <v>0.08689411060257202</v>
       </c>
       <c r="T16">
-        <v>0.9396565025006507</v>
+        <v>0.9490556721148272</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.8951175881663</v>
+        <v>14.83544308228854</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08012234401218621</v>
+        <v>0.0800208991842532</v>
       </c>
       <c r="C17">
-        <v>20.88492629128466</v>
+        <v>20.6395384056509</v>
       </c>
       <c r="D17">
-        <v>1.970426291284663</v>
+        <v>1.970738405650895</v>
       </c>
       <c r="E17">
-        <v>-4.984500000000001</v>
+        <v>-4.738799999999999</v>
       </c>
       <c r="F17">
-        <v>3.6855</v>
+        <v>3.9312</v>
       </c>
       <c r="G17">
         <v>22.6</v>
@@ -2794,28 +2794,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M17">
-        <v>0.18538065</v>
+        <v>0.19773936</v>
       </c>
       <c r="N17">
-        <v>2.564823431632654</v>
+        <v>2.552464721632654</v>
       </c>
       <c r="O17">
-        <v>0.4360199833775512</v>
+        <v>0.4339190026775512</v>
       </c>
       <c r="P17">
-        <v>2.128803448255102</v>
+        <v>2.118545718955103</v>
       </c>
       <c r="Q17">
-        <v>9.888803448255103</v>
+        <v>9.878545718955102</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08689411060257202</v>
+        <v>0.08731078474315858</v>
       </c>
       <c r="T17">
-        <v>0.9490556721148272</v>
+        <v>0.9586786314817224</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.83544308228855</v>
+        <v>13.90822788964551</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0800208991842532</v>
+        <v>0.0799194543563202</v>
       </c>
       <c r="C18">
-        <v>20.6395384056509</v>
+        <v>20.39415061891026</v>
       </c>
       <c r="D18">
-        <v>1.970738405650895</v>
+        <v>1.971050618910255</v>
       </c>
       <c r="E18">
-        <v>-4.738799999999999</v>
+        <v>-4.493099999999999</v>
       </c>
       <c r="F18">
-        <v>3.9312</v>
+        <v>4.176900000000001</v>
       </c>
       <c r="G18">
         <v>22.6</v>
@@ -2876,28 +2876,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M18">
-        <v>0.19773936</v>
+        <v>0.21009807</v>
       </c>
       <c r="N18">
-        <v>2.552464721632654</v>
+        <v>2.540106011632654</v>
       </c>
       <c r="O18">
-        <v>0.4339190026775512</v>
+        <v>0.4318180219775511</v>
       </c>
       <c r="P18">
-        <v>2.118545718955103</v>
+        <v>2.108287989655103</v>
       </c>
       <c r="Q18">
-        <v>9.878545718955102</v>
+        <v>9.868287989655103</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08731078474315858</v>
+        <v>0.08773749922448217</v>
       </c>
       <c r="T18">
-        <v>0.9586786314817224</v>
+        <v>0.9685334693875789</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.90822788964551</v>
+        <v>13.09009683731342</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0799194543563202</v>
+        <v>0.08004210952838718</v>
       </c>
       <c r="C19">
-        <v>20.39415061891026</v>
+        <v>20.1480731398055</v>
       </c>
       <c r="D19">
-        <v>1.971050618910255</v>
+        <v>1.970673139805505</v>
       </c>
       <c r="E19">
-        <v>-4.493099999999999</v>
+        <v>-4.247399999999999</v>
       </c>
       <c r="F19">
-        <v>4.176900000000001</v>
+        <v>4.422600000000001</v>
       </c>
       <c r="G19">
         <v>22.6</v>
@@ -2958,45 +2958,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M19">
-        <v>0.21009807</v>
+        <v>0.22909068</v>
       </c>
       <c r="N19">
-        <v>2.540106011632654</v>
+        <v>2.521113401632654</v>
       </c>
       <c r="O19">
-        <v>0.4318180219775511</v>
+        <v>0.4285892782775511</v>
       </c>
       <c r="P19">
-        <v>2.108287989655103</v>
+        <v>2.092524123355102</v>
       </c>
       <c r="Q19">
-        <v>9.868287989655103</v>
+        <v>9.852524123355103</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08773749922448217</v>
+        <v>0.08817462137608194</v>
       </c>
       <c r="T19">
-        <v>0.9685334693875789</v>
+        <v>0.9786286691935783</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.17</v>
       </c>
       <c r="W19">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.09009683731342</v>
+        <v>12.00487109136283</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0800421095283872</v>
+        <v>0.07995311470045419</v>
       </c>
       <c r="C20">
-        <v>20.14807313980551</v>
+        <v>19.90264701266053</v>
       </c>
       <c r="D20">
-        <v>1.970673139805505</v>
+        <v>1.970947012660532</v>
       </c>
       <c r="E20">
-        <v>-4.2474</v>
+        <v>-4.0017</v>
       </c>
       <c r="F20">
-        <v>4.4226</v>
+        <v>4.6683</v>
       </c>
       <c r="G20">
         <v>22.6</v>
@@ -3040,28 +3040,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M20">
-        <v>0.22909068</v>
+        <v>0.24181794</v>
       </c>
       <c r="N20">
-        <v>2.521113401632654</v>
+        <v>2.508386141632654</v>
       </c>
       <c r="O20">
-        <v>0.4285892782775511</v>
+        <v>0.4264256440775512</v>
       </c>
       <c r="P20">
-        <v>2.092524123355102</v>
+        <v>2.081960497555102</v>
       </c>
       <c r="Q20">
-        <v>9.852524123355103</v>
+        <v>9.841960497555103</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08817462137608194</v>
+        <v>0.08862253666722739</v>
       </c>
       <c r="T20">
-        <v>0.9786286691935783</v>
+        <v>0.9889731331923185</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.00487109136283</v>
+        <v>11.37303577076479</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07995311470045419</v>
+        <v>0.07986411987252119</v>
       </c>
       <c r="C21">
-        <v>19.90264701266053</v>
+        <v>19.6572209616487</v>
       </c>
       <c r="D21">
-        <v>1.970947012660532</v>
+        <v>1.971220961648699</v>
       </c>
       <c r="E21">
-        <v>-4.0017</v>
+        <v>-3.755999999999999</v>
       </c>
       <c r="F21">
-        <v>4.6683</v>
+        <v>4.914000000000001</v>
       </c>
       <c r="G21">
         <v>22.6</v>
@@ -3122,28 +3122,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M21">
-        <v>0.24181794</v>
+        <v>0.2545452</v>
       </c>
       <c r="N21">
-        <v>2.508386141632654</v>
+        <v>2.495658881632654</v>
       </c>
       <c r="O21">
-        <v>0.4264256440775512</v>
+        <v>0.4242620098775511</v>
       </c>
       <c r="P21">
-        <v>2.081960497555102</v>
+        <v>2.071396871755103</v>
       </c>
       <c r="Q21">
-        <v>9.841960497555103</v>
+        <v>9.831396871755103</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08862253666722739</v>
+        <v>0.08908164984065148</v>
       </c>
       <c r="T21">
-        <v>0.9889731331923185</v>
+        <v>0.999576208791027</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.37303577076479</v>
+        <v>10.80438398222655</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07986411987252119</v>
+        <v>0.07977512504458817</v>
       </c>
       <c r="C22">
-        <v>19.6572209616487</v>
+        <v>19.41179498680176</v>
       </c>
       <c r="D22">
-        <v>1.971220961648699</v>
+        <v>1.971494986801754</v>
       </c>
       <c r="E22">
-        <v>-3.755999999999999</v>
+        <v>-3.510299999999999</v>
       </c>
       <c r="F22">
-        <v>4.914000000000001</v>
+        <v>5.159700000000001</v>
       </c>
       <c r="G22">
         <v>22.6</v>
@@ -3204,28 +3204,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M22">
-        <v>0.2545452</v>
+        <v>0.26727246</v>
       </c>
       <c r="N22">
-        <v>2.495658881632654</v>
+        <v>2.482931621632654</v>
       </c>
       <c r="O22">
-        <v>0.4242620098775511</v>
+        <v>0.4220983756775512</v>
       </c>
       <c r="P22">
-        <v>2.071396871755103</v>
+        <v>2.060833245955102</v>
       </c>
       <c r="Q22">
-        <v>9.831396871755103</v>
+        <v>9.820833245955104</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08908164984065148</v>
+        <v>0.08955238613239008</v>
       </c>
       <c r="T22">
-        <v>0.999576208791027</v>
+        <v>1.010447716683374</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.80438398222655</v>
+        <v>10.28988950688243</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07977512504458817</v>
+        <v>0.07968613021665516</v>
       </c>
       <c r="C23">
-        <v>19.41179498680176</v>
+        <v>19.16636908815147</v>
       </c>
       <c r="D23">
-        <v>1.971494986801754</v>
+        <v>1.971769088151468</v>
       </c>
       <c r="E23">
-        <v>-3.5103</v>
+        <v>-3.2646</v>
       </c>
       <c r="F23">
-        <v>5.1597</v>
+        <v>5.4054</v>
       </c>
       <c r="G23">
         <v>22.6</v>
@@ -3286,28 +3286,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M23">
-        <v>0.26727246</v>
+        <v>0.27999972</v>
       </c>
       <c r="N23">
-        <v>2.482931621632654</v>
+        <v>2.470204361632653</v>
       </c>
       <c r="O23">
-        <v>0.4220983756775512</v>
+        <v>0.4199347414775511</v>
       </c>
       <c r="P23">
-        <v>2.060833245955102</v>
+        <v>2.050269620155103</v>
       </c>
       <c r="Q23">
-        <v>9.820833245955104</v>
+        <v>9.810269620155104</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08955238613239008</v>
+        <v>0.09003519258545534</v>
       </c>
       <c r="T23">
-        <v>1.010447716683374</v>
+        <v>1.021597981188345</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.28988950688243</v>
+        <v>9.822167256569591</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07968613021665516</v>
+        <v>0.07992166538872215</v>
       </c>
       <c r="C24">
-        <v>19.16636908815147</v>
+        <v>18.9199438130373</v>
       </c>
       <c r="D24">
-        <v>1.971769088151468</v>
+        <v>1.971043813037295</v>
       </c>
       <c r="E24">
-        <v>-3.2646</v>
+        <v>-3.018899999999999</v>
       </c>
       <c r="F24">
-        <v>5.4054</v>
+        <v>5.6511</v>
       </c>
       <c r="G24">
         <v>22.6</v>
@@ -3368,45 +3368,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M24">
-        <v>0.27999972</v>
+        <v>0.30233385</v>
       </c>
       <c r="N24">
-        <v>2.470204361632653</v>
+        <v>2.447870231632653</v>
       </c>
       <c r="O24">
-        <v>0.4199347414775511</v>
+        <v>0.4161379393775511</v>
       </c>
       <c r="P24">
-        <v>2.050269620155103</v>
+        <v>2.031732292255102</v>
       </c>
       <c r="Q24">
-        <v>9.810269620155104</v>
+        <v>9.791732292255103</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09003519258545534</v>
+        <v>0.09053053946587292</v>
       </c>
       <c r="T24">
-        <v>1.021597981188345</v>
+        <v>1.033037862953185</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.17</v>
       </c>
       <c r="W24">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.822167256569591</v>
+        <v>9.096580093934746</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07992166538872215</v>
+        <v>0.07984678056078914</v>
       </c>
       <c r="C25">
-        <v>18.9199438130373</v>
+        <v>18.67447434537789</v>
       </c>
       <c r="D25">
-        <v>1.971043813037295</v>
+        <v>1.971274345377889</v>
       </c>
       <c r="E25">
-        <v>-3.018899999999999</v>
+        <v>-2.773199999999999</v>
       </c>
       <c r="F25">
-        <v>5.6511</v>
+        <v>5.896800000000001</v>
       </c>
       <c r="G25">
         <v>22.6</v>
@@ -3450,28 +3450,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M25">
-        <v>0.30233385</v>
+        <v>0.3154788000000001</v>
       </c>
       <c r="N25">
-        <v>2.447870231632653</v>
+        <v>2.434725281632653</v>
       </c>
       <c r="O25">
-        <v>0.4161379393775511</v>
+        <v>0.4139032978775511</v>
       </c>
       <c r="P25">
-        <v>2.031732292255102</v>
+        <v>2.020821983755102</v>
       </c>
       <c r="Q25">
-        <v>9.791732292255103</v>
+        <v>9.780821983755104</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09053053946587292</v>
+        <v>0.09103892179051203</v>
       </c>
       <c r="T25">
-        <v>1.033037862953185</v>
+        <v>1.044778794238153</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.096580093934746</v>
+        <v>8.71755592335413</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07984678056078914</v>
+        <v>0.07977189573285612</v>
       </c>
       <c r="C26">
-        <v>18.67447434537789</v>
+        <v>18.4290049316507</v>
       </c>
       <c r="D26">
-        <v>1.971274345377889</v>
+        <v>1.971504931650696</v>
       </c>
       <c r="E26">
-        <v>-2.7732</v>
+        <v>-2.5275</v>
       </c>
       <c r="F26">
-        <v>5.8968</v>
+        <v>6.1425</v>
       </c>
       <c r="G26">
         <v>22.6</v>
@@ -3532,28 +3532,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M26">
-        <v>0.3154788</v>
+        <v>0.32862375</v>
       </c>
       <c r="N26">
-        <v>2.434725281632653</v>
+        <v>2.421580331632653</v>
       </c>
       <c r="O26">
-        <v>0.4139032978775511</v>
+        <v>0.4116686563775511</v>
       </c>
       <c r="P26">
-        <v>2.020821983755102</v>
+        <v>2.009911675255102</v>
       </c>
       <c r="Q26">
-        <v>9.780821983755104</v>
+        <v>9.769911675255102</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09103892179051203</v>
+        <v>0.0915608609771415</v>
       </c>
       <c r="T26">
-        <v>1.044778794238153</v>
+        <v>1.056832817024053</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.717555923354132</v>
+        <v>8.368853686419968</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07977189573285612</v>
+        <v>0.07969701090492312</v>
       </c>
       <c r="C27">
-        <v>18.4290049316507</v>
+        <v>18.18353557187464</v>
       </c>
       <c r="D27">
-        <v>1.971504931650696</v>
+        <v>1.971735571874642</v>
       </c>
       <c r="E27">
-        <v>-2.5275</v>
+        <v>-2.2818</v>
       </c>
       <c r="F27">
-        <v>6.1425</v>
+        <v>6.3882</v>
       </c>
       <c r="G27">
         <v>22.6</v>
@@ -3614,28 +3614,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M27">
-        <v>0.32862375</v>
+        <v>0.3417687</v>
       </c>
       <c r="N27">
-        <v>2.421580331632653</v>
+        <v>2.408435381632653</v>
       </c>
       <c r="O27">
-        <v>0.4116686563775511</v>
+        <v>0.4094340148775511</v>
       </c>
       <c r="P27">
-        <v>2.009911675255102</v>
+        <v>1.999001366755102</v>
       </c>
       <c r="Q27">
-        <v>9.769911675255102</v>
+        <v>9.759001366755102</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0915608609771415</v>
+        <v>0.09209690662827449</v>
       </c>
       <c r="T27">
-        <v>1.056832817024053</v>
+        <v>1.069212624209573</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.368853686419968</v>
+        <v>8.046974698480735</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07969701090492312</v>
+        <v>0.07962212607699011</v>
       </c>
       <c r="C28">
-        <v>18.18353557187464</v>
+        <v>17.93806626606867</v>
       </c>
       <c r="D28">
-        <v>1.971735571874642</v>
+        <v>1.971966266068666</v>
       </c>
       <c r="E28">
-        <v>-2.2818</v>
+        <v>-2.036099999999999</v>
       </c>
       <c r="F28">
-        <v>6.3882</v>
+        <v>6.633900000000001</v>
       </c>
       <c r="G28">
         <v>22.6</v>
@@ -3696,28 +3696,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M28">
-        <v>0.3417687</v>
+        <v>0.35491365</v>
       </c>
       <c r="N28">
-        <v>2.408435381632653</v>
+        <v>2.395290431632654</v>
       </c>
       <c r="O28">
-        <v>0.4094340148775511</v>
+        <v>0.4071993733775512</v>
       </c>
       <c r="P28">
-        <v>1.999001366755102</v>
+        <v>1.988091058255103</v>
       </c>
       <c r="Q28">
-        <v>9.759001366755102</v>
+        <v>9.748091058255103</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09209690662827449</v>
+        <v>0.09264763846163029</v>
       </c>
       <c r="T28">
-        <v>1.069212624209573</v>
+        <v>1.081931604194695</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.046974698480735</v>
+        <v>7.748938598537007</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07962212607699011</v>
+        <v>0.07973316124905711</v>
       </c>
       <c r="C29">
-        <v>17.93806626606867</v>
+        <v>17.69202422451363</v>
       </c>
       <c r="D29">
-        <v>1.971966266068666</v>
+        <v>1.97162422451363</v>
       </c>
       <c r="E29">
-        <v>-2.036099999999999</v>
+        <v>-1.790399999999999</v>
       </c>
       <c r="F29">
-        <v>6.633900000000001</v>
+        <v>6.879600000000001</v>
       </c>
       <c r="G29">
         <v>22.6</v>
@@ -3778,45 +3778,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M29">
-        <v>0.35491365</v>
+        <v>0.37356228</v>
       </c>
       <c r="N29">
-        <v>2.395290431632654</v>
+        <v>2.376641801632654</v>
       </c>
       <c r="O29">
-        <v>0.4071993733775512</v>
+        <v>0.4040291062775512</v>
       </c>
       <c r="P29">
-        <v>1.988091058255103</v>
+        <v>1.972612695355103</v>
       </c>
       <c r="Q29">
-        <v>9.748091058255103</v>
+        <v>9.732612695355103</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09264763846163029</v>
+        <v>0.09321366840146821</v>
       </c>
       <c r="T29">
-        <v>1.081931604194695</v>
+        <v>1.095003889179404</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.17</v>
       </c>
       <c r="W29">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.748938598537007</v>
+        <v>7.362103265973892</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07973316124905711</v>
+        <v>0.07966491642112411</v>
       </c>
       <c r="C30">
-        <v>17.69202422451363</v>
+        <v>17.44653443724307</v>
       </c>
       <c r="D30">
-        <v>1.97162422451363</v>
+        <v>1.971834437243076</v>
       </c>
       <c r="E30">
-        <v>-1.790399999999999</v>
+        <v>-1.544699999999999</v>
       </c>
       <c r="F30">
-        <v>6.879600000000001</v>
+        <v>7.125300000000001</v>
       </c>
       <c r="G30">
         <v>22.6</v>
@@ -3860,28 +3860,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M30">
-        <v>0.37356228</v>
+        <v>0.3869037900000001</v>
       </c>
       <c r="N30">
-        <v>2.376641801632654</v>
+        <v>2.363300291632654</v>
       </c>
       <c r="O30">
-        <v>0.4040291062775512</v>
+        <v>0.4017610495775512</v>
       </c>
       <c r="P30">
-        <v>1.972612695355103</v>
+        <v>1.961539242055103</v>
       </c>
       <c r="Q30">
-        <v>9.732612695355103</v>
+        <v>9.721539242055103</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09321366840146821</v>
+        <v>0.09379564284665366</v>
       </c>
       <c r="T30">
-        <v>1.095003889179404</v>
+        <v>1.108444407543965</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.362103265973892</v>
+        <v>7.108237636112722</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0796649164211241</v>
+        <v>0.07959667159319109</v>
       </c>
       <c r="C31">
-        <v>17.44653443724308</v>
+        <v>17.20104469480267</v>
       </c>
       <c r="D31">
-        <v>1.971834437243076</v>
+        <v>1.97204469480267</v>
       </c>
       <c r="E31">
-        <v>-1.544700000000001</v>
+        <v>-1.299</v>
       </c>
       <c r="F31">
-        <v>7.125299999999999</v>
+        <v>7.371</v>
       </c>
       <c r="G31">
         <v>22.6</v>
@@ -3942,28 +3942,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M31">
-        <v>0.38690379</v>
+        <v>0.4002453</v>
       </c>
       <c r="N31">
-        <v>2.363300291632654</v>
+        <v>2.349958781632654</v>
       </c>
       <c r="O31">
-        <v>0.4017610495775512</v>
+        <v>0.3994929928775511</v>
       </c>
       <c r="P31">
-        <v>1.961539242055103</v>
+        <v>1.950465788755102</v>
       </c>
       <c r="Q31">
-        <v>9.721539242055103</v>
+        <v>9.710465788755103</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09379564284665366</v>
+        <v>0.09439424513313013</v>
       </c>
       <c r="T31">
-        <v>1.108444407543965</v>
+        <v>1.122268940718941</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.108237636112724</v>
+        <v>6.871296381575633</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07959667159319109</v>
+        <v>0.07952842676525808</v>
       </c>
       <c r="C32">
-        <v>17.20104469480267</v>
+        <v>16.95555499720675</v>
       </c>
       <c r="D32">
-        <v>1.97204469480267</v>
+        <v>1.972254997206755</v>
       </c>
       <c r="E32">
-        <v>-1.299</v>
+        <v>-1.0533</v>
       </c>
       <c r="F32">
-        <v>7.371</v>
+        <v>7.6167</v>
       </c>
       <c r="G32">
         <v>22.6</v>
@@ -4024,28 +4024,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M32">
-        <v>0.4002453</v>
+        <v>0.41358681</v>
       </c>
       <c r="N32">
-        <v>2.349958781632654</v>
+        <v>2.336617271632654</v>
       </c>
       <c r="O32">
-        <v>0.3994929928775511</v>
+        <v>0.3972249361775512</v>
       </c>
       <c r="P32">
-        <v>1.950465788755102</v>
+        <v>1.939392335455103</v>
       </c>
       <c r="Q32">
-        <v>9.710465788755103</v>
+        <v>9.699392335455103</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09439424513313013</v>
+        <v>0.09501019821051895</v>
       </c>
       <c r="T32">
-        <v>1.122268940718941</v>
+        <v>1.136494185000438</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.871296381575633</v>
+        <v>6.649641659589323</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07952842676525808</v>
+        <v>0.07946018193732507</v>
       </c>
       <c r="C33">
-        <v>16.95555499720675</v>
+        <v>16.71006534446968</v>
       </c>
       <c r="D33">
-        <v>1.972254997206755</v>
+        <v>1.97246534446968</v>
       </c>
       <c r="E33">
-        <v>-1.0533</v>
+        <v>-0.8075999999999999</v>
       </c>
       <c r="F33">
-        <v>7.6167</v>
+        <v>7.8624</v>
       </c>
       <c r="G33">
         <v>22.6</v>
@@ -4106,28 +4106,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M33">
-        <v>0.41358681</v>
+        <v>0.42692832</v>
       </c>
       <c r="N33">
-        <v>2.336617271632654</v>
+        <v>2.323275761632654</v>
       </c>
       <c r="O33">
-        <v>0.3972249361775512</v>
+        <v>0.3949568794775511</v>
       </c>
       <c r="P33">
-        <v>1.939392335455103</v>
+        <v>1.928318882155102</v>
       </c>
       <c r="Q33">
-        <v>9.699392335455103</v>
+        <v>9.688318882155103</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09501019821051895</v>
+        <v>0.09564426755488982</v>
       </c>
       <c r="T33">
-        <v>1.136494185000438</v>
+        <v>1.151137818819626</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.649641659589323</v>
+        <v>6.441840357727155</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07946018193732507</v>
+        <v>0.07939193710939207</v>
       </c>
       <c r="C34">
-        <v>16.71006534446968</v>
+        <v>16.4645757366058</v>
       </c>
       <c r="D34">
-        <v>1.97246534446968</v>
+        <v>1.972675736605799</v>
       </c>
       <c r="E34">
-        <v>-0.8075999999999999</v>
+        <v>-0.5618999999999996</v>
       </c>
       <c r="F34">
-        <v>7.8624</v>
+        <v>8.1081</v>
       </c>
       <c r="G34">
         <v>22.6</v>
@@ -4188,28 +4188,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M34">
-        <v>0.42692832</v>
+        <v>0.44026983</v>
       </c>
       <c r="N34">
-        <v>2.323275761632654</v>
+        <v>2.309934251632654</v>
       </c>
       <c r="O34">
-        <v>0.3949568794775511</v>
+        <v>0.3926888227775511</v>
       </c>
       <c r="P34">
-        <v>1.928318882155102</v>
+        <v>1.917245428855102</v>
       </c>
       <c r="Q34">
-        <v>9.688318882155103</v>
+        <v>9.677245428855104</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09564426755488982</v>
+        <v>0.09629726434237623</v>
       </c>
       <c r="T34">
-        <v>1.151137818819626</v>
+        <v>1.166218576036403</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.441840357727155</v>
+        <v>6.246633074159666</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07939193710939207</v>
+        <v>0.07960589228145906</v>
       </c>
       <c r="C35">
-        <v>16.4645757366058</v>
+        <v>16.21821628388474</v>
       </c>
       <c r="D35">
-        <v>1.972675736605799</v>
+        <v>1.972016283884738</v>
       </c>
       <c r="E35">
-        <v>-0.5618999999999996</v>
+        <v>-0.3161999999999985</v>
       </c>
       <c r="F35">
-        <v>8.1081</v>
+        <v>8.353800000000001</v>
       </c>
       <c r="G35">
         <v>22.6</v>
@@ -4270,45 +4270,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M35">
-        <v>0.44026983</v>
+        <v>0.4619651400000001</v>
       </c>
       <c r="N35">
-        <v>2.309934251632654</v>
+        <v>2.288238941632653</v>
       </c>
       <c r="O35">
-        <v>0.3926888227775511</v>
+        <v>0.3890006200775511</v>
       </c>
       <c r="P35">
-        <v>1.917245428855102</v>
+        <v>1.899238321555102</v>
       </c>
       <c r="Q35">
-        <v>9.677245428855104</v>
+        <v>9.659238321555103</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09629726434237623</v>
+        <v>0.09697004891130161</v>
       </c>
       <c r="T35">
-        <v>1.166218576036403</v>
+        <v>1.181756325896111</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.17</v>
       </c>
       <c r="W35">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.246633074159666</v>
+        <v>5.953271888940912</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07960589228145906</v>
+        <v>0.07954594745352604</v>
       </c>
       <c r="C36">
-        <v>16.21821628388474</v>
+        <v>15.97270100139455</v>
       </c>
       <c r="D36">
-        <v>1.972016283884738</v>
+        <v>1.972201001394549</v>
       </c>
       <c r="E36">
-        <v>-0.3161999999999985</v>
+        <v>-0.07049999999999912</v>
       </c>
       <c r="F36">
-        <v>8.353800000000001</v>
+        <v>8.599500000000001</v>
       </c>
       <c r="G36">
         <v>22.6</v>
@@ -4352,28 +4352,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M36">
-        <v>0.4619651400000001</v>
+        <v>0.4755523500000001</v>
       </c>
       <c r="N36">
-        <v>2.288238941632653</v>
+        <v>2.274651731632654</v>
       </c>
       <c r="O36">
-        <v>0.3890006200775511</v>
+        <v>0.3866907943775511</v>
       </c>
       <c r="P36">
-        <v>1.899238321555102</v>
+        <v>1.887960937255103</v>
       </c>
       <c r="Q36">
-        <v>9.659238321555103</v>
+        <v>9.647960937255103</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09697004891130161</v>
+        <v>0.09766353454388624</v>
       </c>
       <c r="T36">
-        <v>1.181756325896111</v>
+        <v>1.197772160366888</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.953271888940912</v>
+        <v>5.783178406399744</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07954594745352604</v>
+        <v>0.07948600262559304</v>
       </c>
       <c r="C37">
-        <v>15.97270100139455</v>
+        <v>15.72718575351234</v>
       </c>
       <c r="D37">
-        <v>1.972201001394549</v>
+        <v>1.972385753512345</v>
       </c>
       <c r="E37">
-        <v>-0.07049999999999912</v>
+        <v>0.175200000000002</v>
       </c>
       <c r="F37">
-        <v>8.599500000000001</v>
+        <v>8.845200000000002</v>
       </c>
       <c r="G37">
         <v>22.6</v>
@@ -4434,28 +4434,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M37">
-        <v>0.4755523500000001</v>
+        <v>0.4891395600000001</v>
       </c>
       <c r="N37">
-        <v>2.274651731632654</v>
+        <v>2.261064521632654</v>
       </c>
       <c r="O37">
-        <v>0.3866907943775511</v>
+        <v>0.3843809686775512</v>
       </c>
       <c r="P37">
-        <v>1.887960937255103</v>
+        <v>1.876683552955102</v>
       </c>
       <c r="Q37">
-        <v>9.647960937255103</v>
+        <v>9.636683552955104</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09766353454388624</v>
+        <v>0.09837869160248913</v>
       </c>
       <c r="T37">
-        <v>1.197772160366888</v>
+        <v>1.214288489664876</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.783178406399744</v>
+        <v>5.622534561777528</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07948600262559305</v>
+        <v>0.07942605779766004</v>
       </c>
       <c r="C38">
-        <v>15.72718575351235</v>
+        <v>15.48167054024785</v>
       </c>
       <c r="D38">
-        <v>1.972385753512345</v>
+        <v>1.972570540247853</v>
       </c>
       <c r="E38">
-        <v>0.1752000000000002</v>
+        <v>0.4208999999999996</v>
       </c>
       <c r="F38">
-        <v>8.8452</v>
+        <v>9.0909</v>
       </c>
       <c r="G38">
         <v>22.6</v>
@@ -4516,28 +4516,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M38">
-        <v>0.48913956</v>
+        <v>0.50272677</v>
       </c>
       <c r="N38">
-        <v>2.261064521632654</v>
+        <v>2.247477311632654</v>
       </c>
       <c r="O38">
-        <v>0.3843809686775512</v>
+        <v>0.3820711429775512</v>
       </c>
       <c r="P38">
-        <v>1.876683552955102</v>
+        <v>1.865406168655103</v>
       </c>
       <c r="Q38">
-        <v>9.636683552955104</v>
+        <v>9.625406168655104</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09837869160248913</v>
+        <v>0.09911655205977785</v>
       </c>
       <c r="T38">
-        <v>1.214288489664876</v>
+        <v>1.231329146877086</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.622534561777529</v>
+        <v>5.470574168215975</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07942605779766004</v>
+        <v>0.07936611296972704</v>
       </c>
       <c r="C39">
-        <v>15.48167054024785</v>
+        <v>15.2361553616108</v>
       </c>
       <c r="D39">
-        <v>1.972570540247853</v>
+        <v>1.972755361610803</v>
       </c>
       <c r="E39">
-        <v>0.4208999999999996</v>
+        <v>0.6666000000000007</v>
       </c>
       <c r="F39">
-        <v>9.0909</v>
+        <v>9.336600000000001</v>
       </c>
       <c r="G39">
         <v>22.6</v>
@@ -4598,28 +4598,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M39">
-        <v>0.50272677</v>
+        <v>0.5163139800000001</v>
       </c>
       <c r="N39">
-        <v>2.247477311632654</v>
+        <v>2.233890101632654</v>
       </c>
       <c r="O39">
-        <v>0.3820711429775512</v>
+        <v>0.3797613172775511</v>
       </c>
       <c r="P39">
-        <v>1.865406168655103</v>
+        <v>1.854128784355102</v>
       </c>
       <c r="Q39">
-        <v>9.625406168655104</v>
+        <v>9.614128784355103</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09911655205977785</v>
+        <v>0.09987821446730166</v>
       </c>
       <c r="T39">
-        <v>1.231329146877086</v>
+        <v>1.248919502709045</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.470574168215975</v>
+        <v>5.326611690105027</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07936611296972704</v>
+        <v>0.079306168141794</v>
       </c>
       <c r="C40">
-        <v>15.2361553616108</v>
+        <v>14.99064021761093</v>
       </c>
       <c r="D40">
-        <v>1.972755361610803</v>
+        <v>1.972940217610929</v>
       </c>
       <c r="E40">
-        <v>0.6666000000000007</v>
+        <v>0.9123000000000001</v>
       </c>
       <c r="F40">
-        <v>9.336600000000001</v>
+        <v>9.5823</v>
       </c>
       <c r="G40">
         <v>22.6</v>
@@ -4680,28 +4680,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M40">
-        <v>0.5163139800000001</v>
+        <v>0.52990119</v>
       </c>
       <c r="N40">
-        <v>2.233890101632654</v>
+        <v>2.220302891632654</v>
       </c>
       <c r="O40">
-        <v>0.3797613172775511</v>
+        <v>0.3774514915775511</v>
       </c>
       <c r="P40">
-        <v>1.854128784355102</v>
+        <v>1.842851400055103</v>
       </c>
       <c r="Q40">
-        <v>9.614128784355103</v>
+        <v>9.602851400055103</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09987821446730166</v>
+        <v>0.1006648494127771</v>
       </c>
       <c r="T40">
-        <v>1.248919502709045</v>
+        <v>1.267086591519101</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.326611690105027</v>
+        <v>5.190031903179258</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.079306168141794</v>
+        <v>0.079246223313861</v>
       </c>
       <c r="C41">
-        <v>14.99064021761093</v>
+        <v>14.74512510825797</v>
       </c>
       <c r="D41">
-        <v>1.972940217610929</v>
+        <v>1.97312510825797</v>
       </c>
       <c r="E41">
-        <v>0.9123000000000001</v>
+        <v>1.158000000000001</v>
       </c>
       <c r="F41">
-        <v>9.5823</v>
+        <v>9.828000000000001</v>
       </c>
       <c r="G41">
         <v>22.6</v>
@@ -4762,28 +4762,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M41">
-        <v>0.52990119</v>
+        <v>0.5434884000000001</v>
       </c>
       <c r="N41">
-        <v>2.220302891632654</v>
+        <v>2.206715681632653</v>
       </c>
       <c r="O41">
-        <v>0.3774514915775511</v>
+        <v>0.3751416658775511</v>
       </c>
       <c r="P41">
-        <v>1.842851400055103</v>
+        <v>1.831574015755102</v>
       </c>
       <c r="Q41">
-        <v>9.602851400055103</v>
+        <v>9.591574015755103</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1006648494127771</v>
+        <v>0.1014777055231017</v>
       </c>
       <c r="T41">
-        <v>1.267086591519101</v>
+        <v>1.285859249956159</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.190031903179258</v>
+        <v>5.060281105599776</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.079246223313861</v>
+        <v>0.079186278485928</v>
       </c>
       <c r="C42">
-        <v>14.74512510825797</v>
+        <v>14.49961003356167</v>
       </c>
       <c r="D42">
-        <v>1.97312510825797</v>
+        <v>1.973310033561668</v>
       </c>
       <c r="E42">
-        <v>1.158000000000001</v>
+        <v>1.403700000000001</v>
       </c>
       <c r="F42">
-        <v>9.828000000000001</v>
+        <v>10.0737</v>
       </c>
       <c r="G42">
         <v>22.6</v>
@@ -4844,28 +4844,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M42">
-        <v>0.5434884000000001</v>
+        <v>0.5570756100000001</v>
       </c>
       <c r="N42">
-        <v>2.206715681632653</v>
+        <v>2.193128471632654</v>
       </c>
       <c r="O42">
-        <v>0.3751416658775511</v>
+        <v>0.3728318401775511</v>
       </c>
       <c r="P42">
-        <v>1.831574015755102</v>
+        <v>1.820296631455102</v>
       </c>
       <c r="Q42">
-        <v>9.591574015755103</v>
+        <v>9.580296631455102</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1014777055231017</v>
+        <v>0.1023181160778441</v>
       </c>
       <c r="T42">
-        <v>1.285859249956159</v>
+        <v>1.305268269696168</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.060281105599776</v>
+        <v>4.936859615219294</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.079186278485928</v>
+        <v>0.07912633365799498</v>
       </c>
       <c r="C43">
-        <v>14.49961003356167</v>
+        <v>14.25409499353177</v>
       </c>
       <c r="D43">
-        <v>1.973310033561668</v>
+        <v>1.973494993531766</v>
       </c>
       <c r="E43">
-        <v>1.403700000000001</v>
+        <v>1.649400000000002</v>
       </c>
       <c r="F43">
-        <v>10.0737</v>
+        <v>10.3194</v>
       </c>
       <c r="G43">
         <v>22.6</v>
@@ -4926,28 +4926,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M43">
-        <v>0.5570756100000001</v>
+        <v>0.5706628200000001</v>
       </c>
       <c r="N43">
-        <v>2.193128471632654</v>
+        <v>2.179541261632654</v>
       </c>
       <c r="O43">
-        <v>0.3728318401775511</v>
+        <v>0.3705220144775512</v>
       </c>
       <c r="P43">
-        <v>1.820296631455102</v>
+        <v>1.809019247155103</v>
       </c>
       <c r="Q43">
-        <v>9.580296631455102</v>
+        <v>9.569019247155103</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1023181160778441</v>
+        <v>0.1031875063068879</v>
       </c>
       <c r="T43">
-        <v>1.305268269696168</v>
+        <v>1.325346565978936</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.936859615219294</v>
+        <v>4.819315338666453</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.079126333657995</v>
+        <v>0.07906638883006199</v>
       </c>
       <c r="C44">
-        <v>14.25409499353177</v>
+        <v>14.00857998817802</v>
       </c>
       <c r="D44">
-        <v>1.973494993531766</v>
+        <v>1.973679988178014</v>
       </c>
       <c r="E44">
-        <v>1.6494</v>
+        <v>1.895099999999999</v>
       </c>
       <c r="F44">
-        <v>10.3194</v>
+        <v>10.5651</v>
       </c>
       <c r="G44">
         <v>22.6</v>
@@ -5008,28 +5008,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M44">
-        <v>0.57066282</v>
+        <v>0.58425003</v>
       </c>
       <c r="N44">
-        <v>2.179541261632654</v>
+        <v>2.165954051632654</v>
       </c>
       <c r="O44">
-        <v>0.3705220144775512</v>
+        <v>0.3682121887775512</v>
       </c>
       <c r="P44">
-        <v>1.809019247155103</v>
+        <v>1.797741862855103</v>
       </c>
       <c r="Q44">
-        <v>9.569019247155103</v>
+        <v>9.557741862855103</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1031875063068879</v>
+        <v>0.1040874014562491</v>
       </c>
       <c r="T44">
-        <v>1.325346565978936</v>
+        <v>1.34612936388566</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.819315338666454</v>
+        <v>4.707238237767235</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07906638883006199</v>
+        <v>0.07900644400212897</v>
       </c>
       <c r="C45">
-        <v>14.00857998817802</v>
+        <v>13.76306501751016</v>
       </c>
       <c r="D45">
-        <v>1.973679988178014</v>
+        <v>1.973865017510166</v>
       </c>
       <c r="E45">
-        <v>1.895099999999999</v>
+        <v>2.1408</v>
       </c>
       <c r="F45">
-        <v>10.5651</v>
+        <v>10.8108</v>
       </c>
       <c r="G45">
         <v>22.6</v>
@@ -5090,28 +5090,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M45">
-        <v>0.58425003</v>
+        <v>0.59783724</v>
       </c>
       <c r="N45">
-        <v>2.165954051632654</v>
+        <v>2.152366841632654</v>
       </c>
       <c r="O45">
-        <v>0.3682121887775512</v>
+        <v>0.3659023630775511</v>
       </c>
       <c r="P45">
-        <v>1.797741862855103</v>
+        <v>1.786464478555102</v>
       </c>
       <c r="Q45">
-        <v>9.557741862855103</v>
+        <v>9.546464478555103</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1040874014562491</v>
+        <v>0.1050194357180874</v>
       </c>
       <c r="T45">
-        <v>1.34612936388566</v>
+        <v>1.367654404574768</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.707238237767235</v>
+        <v>4.600255550545251</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07900644400212897</v>
+        <v>0.07988024917419598</v>
       </c>
       <c r="C46">
-        <v>13.76306501751016</v>
+        <v>13.5146713058562</v>
       </c>
       <c r="D46">
-        <v>1.973865017510166</v>
+        <v>1.971171305856196</v>
       </c>
       <c r="E46">
-        <v>2.1408</v>
+        <v>2.3865</v>
       </c>
       <c r="F46">
-        <v>10.8108</v>
+        <v>11.0565</v>
       </c>
       <c r="G46">
         <v>22.6</v>
@@ -5172,45 +5172,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M46">
-        <v>0.59783724</v>
+        <v>0.6390657000000001</v>
       </c>
       <c r="N46">
-        <v>2.152366841632654</v>
+        <v>2.111138381632653</v>
       </c>
       <c r="O46">
-        <v>0.3659023630775511</v>
+        <v>0.3588935248775511</v>
       </c>
       <c r="P46">
-        <v>1.786464478555102</v>
+        <v>1.752244856755102</v>
       </c>
       <c r="Q46">
-        <v>9.546464478555103</v>
+        <v>9.512244856755103</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1050194357180874</v>
+        <v>0.1059853621349018</v>
       </c>
       <c r="T46">
-        <v>1.367654404574768</v>
+        <v>1.389962174016207</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.17</v>
       </c>
       <c r="W46">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.600255550545251</v>
+        <v>4.303476280502386</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07988024917419598</v>
+        <v>0.07984105434626296</v>
       </c>
       <c r="C47">
-        <v>13.5146713058562</v>
+        <v>13.26909197570271</v>
       </c>
       <c r="D47">
-        <v>1.971171305856196</v>
+        <v>1.971291975702712</v>
       </c>
       <c r="E47">
-        <v>2.3865</v>
+        <v>2.632200000000001</v>
       </c>
       <c r="F47">
-        <v>11.0565</v>
+        <v>11.3022</v>
       </c>
       <c r="G47">
         <v>22.6</v>
@@ -5254,28 +5254,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M47">
-        <v>0.6390657000000001</v>
+        <v>0.6532671600000001</v>
       </c>
       <c r="N47">
-        <v>2.111138381632653</v>
+        <v>2.096936921632654</v>
       </c>
       <c r="O47">
-        <v>0.3588935248775511</v>
+        <v>0.3564792766775511</v>
       </c>
       <c r="P47">
-        <v>1.752244856755102</v>
+        <v>1.740457644955103</v>
       </c>
       <c r="Q47">
-        <v>9.512244856755103</v>
+        <v>9.500457644955103</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1059853621349018</v>
+        <v>0.1069870636041907</v>
       </c>
       <c r="T47">
-        <v>1.389962174016207</v>
+        <v>1.413096157140662</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.303476280502386</v>
+        <v>4.209922448317551</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07984105434626296</v>
+        <v>0.07980185951832997</v>
       </c>
       <c r="C48">
-        <v>13.26909197570271</v>
+        <v>13.02351266032431</v>
       </c>
       <c r="D48">
-        <v>1.971291975702712</v>
+        <v>1.971412660324305</v>
       </c>
       <c r="E48">
-        <v>2.632200000000001</v>
+        <v>2.8779</v>
       </c>
       <c r="F48">
-        <v>11.3022</v>
+        <v>11.5479</v>
       </c>
       <c r="G48">
         <v>22.6</v>
@@ -5336,28 +5336,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M48">
-        <v>0.6532671600000001</v>
+        <v>0.6674686200000001</v>
       </c>
       <c r="N48">
-        <v>2.096936921632654</v>
+        <v>2.082735461632653</v>
       </c>
       <c r="O48">
-        <v>0.3564792766775511</v>
+        <v>0.3540650284775511</v>
       </c>
       <c r="P48">
-        <v>1.740457644955103</v>
+        <v>1.728670433155102</v>
       </c>
       <c r="Q48">
-        <v>9.500457644955103</v>
+        <v>9.488670433155104</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1069870636041907</v>
+        <v>0.1080265651289244</v>
       </c>
       <c r="T48">
-        <v>1.413096157140662</v>
+        <v>1.43710312076038</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.209922448317551</v>
+        <v>4.120349630268241</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07980185951832997</v>
+        <v>0.07976266469039694</v>
       </c>
       <c r="C49">
-        <v>13.02351266032431</v>
+        <v>12.77793335972369</v>
       </c>
       <c r="D49">
-        <v>1.971412660324305</v>
+        <v>1.971533359723687</v>
       </c>
       <c r="E49">
-        <v>2.8779</v>
+        <v>3.123600000000001</v>
       </c>
       <c r="F49">
-        <v>11.5479</v>
+        <v>11.7936</v>
       </c>
       <c r="G49">
         <v>22.6</v>
@@ -5418,28 +5418,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M49">
-        <v>0.6674686200000001</v>
+        <v>0.6816700800000002</v>
       </c>
       <c r="N49">
-        <v>2.082735461632653</v>
+        <v>2.068534001632654</v>
       </c>
       <c r="O49">
-        <v>0.3540650284775511</v>
+        <v>0.3516507802775511</v>
       </c>
       <c r="P49">
-        <v>1.728670433155102</v>
+        <v>1.716883221355102</v>
       </c>
       <c r="Q49">
-        <v>9.488670433155104</v>
+        <v>9.476883221355102</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1080265651289244</v>
+        <v>0.1091060474815326</v>
       </c>
       <c r="T49">
-        <v>1.43710312076038</v>
+        <v>1.462033429134702</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.120349630268241</v>
+        <v>4.034509012970986</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07976266469039694</v>
+        <v>0.08114691986246395</v>
       </c>
       <c r="C50">
-        <v>12.77793335972369</v>
+        <v>12.52797952089219</v>
       </c>
       <c r="D50">
-        <v>1.971533359723687</v>
+        <v>1.967279520892187</v>
       </c>
       <c r="E50">
-        <v>3.1236</v>
+        <v>3.369300000000001</v>
       </c>
       <c r="F50">
-        <v>11.7936</v>
+        <v>12.0393</v>
       </c>
       <c r="G50">
         <v>22.6</v>
@@ -5500,45 +5500,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M50">
-        <v>0.6816700800000001</v>
+        <v>0.73800909</v>
       </c>
       <c r="N50">
-        <v>2.068534001632654</v>
+        <v>2.012194991632653</v>
       </c>
       <c r="O50">
-        <v>0.3516507802775511</v>
+        <v>0.3420731485775511</v>
       </c>
       <c r="P50">
-        <v>1.716883221355102</v>
+        <v>1.670121843055102</v>
       </c>
       <c r="Q50">
-        <v>9.476883221355102</v>
+        <v>9.430121843055103</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1091060474815326</v>
+        <v>0.1102278624754195</v>
       </c>
       <c r="T50">
-        <v>1.462033429134702</v>
+        <v>1.487941396660958</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.17</v>
       </c>
       <c r="W50">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.034509012970986</v>
+        <v>3.726517896456605</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08114691986246395</v>
+        <v>0.08113677503453093</v>
       </c>
       <c r="C51">
-        <v>12.52797952089219</v>
+        <v>12.28231062934202</v>
       </c>
       <c r="D51">
-        <v>1.967279520892187</v>
+        <v>1.967310629342021</v>
       </c>
       <c r="E51">
-        <v>3.369300000000001</v>
+        <v>3.615</v>
       </c>
       <c r="F51">
-        <v>12.0393</v>
+        <v>12.285</v>
       </c>
       <c r="G51">
         <v>22.6</v>
@@ -5582,28 +5582,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M51">
-        <v>0.73800909</v>
+        <v>0.7530705</v>
       </c>
       <c r="N51">
-        <v>2.012194991632653</v>
+        <v>1.997133581632654</v>
       </c>
       <c r="O51">
-        <v>0.3420731485775511</v>
+        <v>0.3395127088775511</v>
       </c>
       <c r="P51">
-        <v>1.670121843055102</v>
+        <v>1.657620872755103</v>
       </c>
       <c r="Q51">
-        <v>9.430121843055103</v>
+        <v>9.417620872755103</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1102278624754195</v>
+        <v>0.1113945500690618</v>
       </c>
       <c r="T51">
-        <v>1.487941396660958</v>
+        <v>1.514885682888265</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.726517896456605</v>
+        <v>3.651987538527473</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08113677503453093</v>
+        <v>0.08112663020659792</v>
       </c>
       <c r="C52">
-        <v>12.28231062934202</v>
+        <v>12.0366417387757</v>
       </c>
       <c r="D52">
-        <v>1.967310629342021</v>
+        <v>1.967341738775702</v>
       </c>
       <c r="E52">
-        <v>3.615</v>
+        <v>3.8607</v>
       </c>
       <c r="F52">
-        <v>12.285</v>
+        <v>12.5307</v>
       </c>
       <c r="G52">
         <v>22.6</v>
@@ -5664,28 +5664,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M52">
-        <v>0.7530705</v>
+        <v>0.76813191</v>
       </c>
       <c r="N52">
-        <v>1.997133581632654</v>
+        <v>1.982072171632653</v>
       </c>
       <c r="O52">
-        <v>0.3395127088775511</v>
+        <v>0.3369522691775511</v>
       </c>
       <c r="P52">
-        <v>1.657620872755103</v>
+        <v>1.645119902455102</v>
       </c>
       <c r="Q52">
-        <v>9.417620872755103</v>
+        <v>9.405119902455104</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1113945500690618</v>
+        <v>0.1126088575644855</v>
       </c>
       <c r="T52">
-        <v>1.514885682888265</v>
+        <v>1.542929735900359</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.651987538527473</v>
+        <v>3.580379939732817</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08112663020659792</v>
+        <v>0.08111648537866491</v>
       </c>
       <c r="C53">
-        <v>12.0366417387757</v>
+        <v>11.79097284919328</v>
       </c>
       <c r="D53">
-        <v>1.967341738775702</v>
+        <v>1.967372849193276</v>
       </c>
       <c r="E53">
-        <v>3.8607</v>
+        <v>4.106400000000001</v>
       </c>
       <c r="F53">
-        <v>12.5307</v>
+        <v>12.7764</v>
       </c>
       <c r="G53">
         <v>22.6</v>
@@ -5746,28 +5746,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M53">
-        <v>0.76813191</v>
+        <v>0.7831933200000001</v>
       </c>
       <c r="N53">
-        <v>1.982072171632653</v>
+        <v>1.967010761632654</v>
       </c>
       <c r="O53">
-        <v>0.3369522691775511</v>
+        <v>0.3343918294775511</v>
       </c>
       <c r="P53">
-        <v>1.645119902455102</v>
+        <v>1.632618932155102</v>
       </c>
       <c r="Q53">
-        <v>9.405119902455104</v>
+        <v>9.392618932155102</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1126088575644855</v>
+        <v>0.1138737612055519</v>
       </c>
       <c r="T53">
-        <v>1.542929735900359</v>
+        <v>1.572142291121291</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.580379939732817</v>
+        <v>3.51152647935334</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08111648537866491</v>
+        <v>0.0823380605507319</v>
       </c>
       <c r="C54">
-        <v>11.79097284919328</v>
+        <v>11.54153379255533</v>
       </c>
       <c r="D54">
-        <v>1.967372849193276</v>
+        <v>1.963633792555326</v>
       </c>
       <c r="E54">
-        <v>4.106400000000001</v>
+        <v>4.3521</v>
       </c>
       <c r="F54">
-        <v>12.7764</v>
+        <v>13.0221</v>
       </c>
       <c r="G54">
         <v>22.6</v>
@@ -5828,45 +5828,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M54">
-        <v>0.7831933200000001</v>
+        <v>0.8347166100000001</v>
       </c>
       <c r="N54">
-        <v>1.967010761632654</v>
+        <v>1.915487471632654</v>
       </c>
       <c r="O54">
-        <v>0.3343918294775511</v>
+        <v>0.3256328701775511</v>
       </c>
       <c r="P54">
-        <v>1.632618932155102</v>
+        <v>1.589854601455102</v>
       </c>
       <c r="Q54">
-        <v>9.392618932155102</v>
+        <v>9.349854601455103</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1138737612055519</v>
+        <v>0.1151924905334721</v>
       </c>
       <c r="T54">
-        <v>1.572142291121291</v>
+        <v>1.602597933798433</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.17</v>
       </c>
       <c r="W54">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.51152647935334</v>
+        <v>3.29477579418559</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0823380605507319</v>
+        <v>0.0823511557227989</v>
       </c>
       <c r="C55">
-        <v>11.54153379255533</v>
+        <v>11.29579378720927</v>
       </c>
       <c r="D55">
-        <v>1.963633792555326</v>
+        <v>1.963593787209273</v>
       </c>
       <c r="E55">
-        <v>4.3521</v>
+        <v>4.597800000000001</v>
       </c>
       <c r="F55">
-        <v>13.0221</v>
+        <v>13.2678</v>
       </c>
       <c r="G55">
         <v>22.6</v>
@@ -5910,28 +5910,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M55">
-        <v>0.8347166100000001</v>
+        <v>0.8504659800000002</v>
       </c>
       <c r="N55">
-        <v>1.915487471632654</v>
+        <v>1.899738101632654</v>
       </c>
       <c r="O55">
-        <v>0.3256328701775511</v>
+        <v>0.3229554772775511</v>
       </c>
       <c r="P55">
-        <v>1.589854601455102</v>
+        <v>1.576782624355102</v>
       </c>
       <c r="Q55">
-        <v>9.349854601455103</v>
+        <v>9.336782624355102</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1151924905334721</v>
+        <v>0.116568555919128</v>
       </c>
       <c r="T55">
-        <v>1.602597933798433</v>
+        <v>1.634377734852841</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.29477579418559</v>
+        <v>3.233761427626597</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0823511557227989</v>
+        <v>0.08236425089486589</v>
       </c>
       <c r="C56">
-        <v>11.29579378720927</v>
+        <v>11.05005378349325</v>
       </c>
       <c r="D56">
-        <v>1.963593787209273</v>
+        <v>1.963553783493255</v>
       </c>
       <c r="E56">
-        <v>4.597800000000001</v>
+        <v>4.843500000000001</v>
       </c>
       <c r="F56">
-        <v>13.2678</v>
+        <v>13.5135</v>
       </c>
       <c r="G56">
         <v>22.6</v>
@@ -5992,28 +5992,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M56">
-        <v>0.8504659800000002</v>
+        <v>0.8662153500000001</v>
       </c>
       <c r="N56">
-        <v>1.899738101632654</v>
+        <v>1.883988731632654</v>
       </c>
       <c r="O56">
-        <v>0.3229554772775511</v>
+        <v>0.3202780843775511</v>
       </c>
       <c r="P56">
-        <v>1.576782624355102</v>
+        <v>1.563710647255102</v>
       </c>
       <c r="Q56">
-        <v>9.336782624355102</v>
+        <v>9.323710647255103</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.116568555919128</v>
+        <v>0.1180057797663686</v>
       </c>
       <c r="T56">
-        <v>1.634377734852841</v>
+        <v>1.667569971509669</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.233761427626597</v>
+        <v>3.174965765306114</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08236425089486589</v>
+        <v>0.08237734606693288</v>
       </c>
       <c r="C57">
-        <v>11.05005378349325</v>
+        <v>10.80431378140717</v>
       </c>
       <c r="D57">
-        <v>1.963553783493255</v>
+        <v>1.963513781407171</v>
       </c>
       <c r="E57">
-        <v>4.843500000000001</v>
+        <v>5.089200000000002</v>
       </c>
       <c r="F57">
-        <v>13.5135</v>
+        <v>13.7592</v>
       </c>
       <c r="G57">
         <v>22.6</v>
@@ -6074,28 +6074,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M57">
-        <v>0.8662153500000001</v>
+        <v>0.8819647200000001</v>
       </c>
       <c r="N57">
-        <v>1.883988731632654</v>
+        <v>1.868239361632654</v>
       </c>
       <c r="O57">
-        <v>0.3202780843775511</v>
+        <v>0.3176006914775512</v>
       </c>
       <c r="P57">
-        <v>1.563710647255102</v>
+        <v>1.550638670155102</v>
       </c>
       <c r="Q57">
-        <v>9.323710647255103</v>
+        <v>9.310638670155104</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1180057797663686</v>
+        <v>0.119508331970302</v>
       </c>
       <c r="T57">
-        <v>1.667569971509669</v>
+        <v>1.702270946196351</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.174965765306114</v>
+        <v>3.118269948068505</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08237734606693288</v>
+        <v>0.08239044123899987</v>
       </c>
       <c r="C58">
-        <v>10.80431378140717</v>
+        <v>10.55857378095092</v>
       </c>
       <c r="D58">
-        <v>1.963513781407171</v>
+        <v>1.963473780950922</v>
       </c>
       <c r="E58">
-        <v>5.089200000000002</v>
+        <v>5.334900000000001</v>
       </c>
       <c r="F58">
-        <v>13.7592</v>
+        <v>14.0049</v>
       </c>
       <c r="G58">
         <v>22.6</v>
@@ -6156,28 +6156,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M58">
-        <v>0.8819647200000001</v>
+        <v>0.8977140900000001</v>
       </c>
       <c r="N58">
-        <v>1.868239361632654</v>
+        <v>1.852489991632654</v>
       </c>
       <c r="O58">
-        <v>0.3176006914775512</v>
+        <v>0.3149232985775511</v>
       </c>
       <c r="P58">
-        <v>1.550638670155102</v>
+        <v>1.537566693055102</v>
       </c>
       <c r="Q58">
-        <v>9.310638670155104</v>
+        <v>9.297566693055103</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.119508331970302</v>
+        <v>0.1210807703232555</v>
       </c>
       <c r="T58">
-        <v>1.702270946196351</v>
+        <v>1.73858591970567</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.118269948068505</v>
+        <v>3.063563457751513</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08239044123899987</v>
+        <v>0.08240353641106685</v>
       </c>
       <c r="C59">
-        <v>10.55857378095092</v>
+        <v>10.31283378212441</v>
       </c>
       <c r="D59">
-        <v>1.963473780950922</v>
+        <v>1.963433782124408</v>
       </c>
       <c r="E59">
-        <v>5.334900000000001</v>
+        <v>5.580600000000002</v>
       </c>
       <c r="F59">
-        <v>14.0049</v>
+        <v>14.2506</v>
       </c>
       <c r="G59">
         <v>22.6</v>
@@ -6238,28 +6238,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M59">
-        <v>0.8977140900000001</v>
+        <v>0.9134634600000002</v>
       </c>
       <c r="N59">
-        <v>1.852489991632654</v>
+        <v>1.836740621632653</v>
       </c>
       <c r="O59">
-        <v>0.3149232985775511</v>
+        <v>0.3122459056775511</v>
       </c>
       <c r="P59">
-        <v>1.537566693055102</v>
+        <v>1.524494715955102</v>
       </c>
       <c r="Q59">
-        <v>9.297566693055103</v>
+        <v>9.284494715955104</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1210807703232555</v>
+        <v>0.1227280866930163</v>
       </c>
       <c r="T59">
-        <v>1.73858591970567</v>
+        <v>1.776630177667814</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.063563457751513</v>
+        <v>3.010743398135108</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08240353641106686</v>
+        <v>0.08623629158313385</v>
       </c>
       <c r="C60">
-        <v>10.31283378212441</v>
+        <v>10.05549636722276</v>
       </c>
       <c r="D60">
-        <v>1.963433782124408</v>
+        <v>1.951796367222756</v>
       </c>
       <c r="E60">
-        <v>5.580599999999999</v>
+        <v>5.8263</v>
       </c>
       <c r="F60">
-        <v>14.2506</v>
+        <v>14.4963</v>
       </c>
       <c r="G60">
         <v>22.6</v>
@@ -6320,45 +6320,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M60">
-        <v>0.91346346</v>
+        <v>1.04228397</v>
       </c>
       <c r="N60">
-        <v>1.836740621632654</v>
+        <v>1.707920111632653</v>
       </c>
       <c r="O60">
-        <v>0.3122459056775511</v>
+        <v>0.2903464189775511</v>
       </c>
       <c r="P60">
-        <v>1.524494715955103</v>
+        <v>1.417573692655102</v>
       </c>
       <c r="Q60">
-        <v>9.284494715955104</v>
+        <v>9.177573692655104</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1227280866930163</v>
+        <v>0.124455759958863</v>
       </c>
       <c r="T60">
-        <v>1.776630177667814</v>
+        <v>1.816530253091525</v>
       </c>
       <c r="U60">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.17</v>
       </c>
       <c r="W60">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.010743398135108</v>
+        <v>2.638632235351996</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08623629158313385</v>
+        <v>0.08631412675520084</v>
       </c>
       <c r="C61">
-        <v>10.05549636722276</v>
+        <v>9.809561464903508</v>
       </c>
       <c r="D61">
-        <v>1.951796367222756</v>
+        <v>1.951561464903505</v>
       </c>
       <c r="E61">
-        <v>5.8263</v>
+        <v>6.071999999999999</v>
       </c>
       <c r="F61">
-        <v>14.4963</v>
+        <v>14.742</v>
       </c>
       <c r="G61">
         <v>22.6</v>
@@ -6402,28 +6402,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M61">
-        <v>1.04228397</v>
+        <v>1.0599498</v>
       </c>
       <c r="N61">
-        <v>1.707920111632653</v>
+        <v>1.690254281632654</v>
       </c>
       <c r="O61">
-        <v>0.2903464189775511</v>
+        <v>0.2873432278775511</v>
       </c>
       <c r="P61">
-        <v>1.417573692655102</v>
+        <v>1.402911053755102</v>
       </c>
       <c r="Q61">
-        <v>9.177573692655104</v>
+        <v>9.162911053755103</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.124455759958863</v>
+        <v>0.1262698168880021</v>
       </c>
       <c r="T61">
-        <v>1.816530253091525</v>
+        <v>1.858425332286423</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.638632235351996</v>
+        <v>2.594655031429463</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08631412675520084</v>
+        <v>0.08639196192726784</v>
       </c>
       <c r="C62">
-        <v>9.809561464903508</v>
+        <v>9.563626619119312</v>
       </c>
       <c r="D62">
-        <v>1.951561464903505</v>
+        <v>1.951326619119311</v>
       </c>
       <c r="E62">
-        <v>6.071999999999999</v>
+        <v>6.3177</v>
       </c>
       <c r="F62">
-        <v>14.742</v>
+        <v>14.9877</v>
       </c>
       <c r="G62">
         <v>22.6</v>
@@ -6484,28 +6484,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M62">
-        <v>1.0599498</v>
+        <v>1.07761563</v>
       </c>
       <c r="N62">
-        <v>1.690254281632654</v>
+        <v>1.672588451632653</v>
       </c>
       <c r="O62">
-        <v>0.2873432278775511</v>
+        <v>0.2843400367775511</v>
       </c>
       <c r="P62">
-        <v>1.402911053755102</v>
+        <v>1.388248414855102</v>
       </c>
       <c r="Q62">
-        <v>9.162911053755103</v>
+        <v>9.148248414855104</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1262698168880021</v>
+        <v>0.1281769023776098</v>
       </c>
       <c r="T62">
-        <v>1.858425332286423</v>
+        <v>1.902468877081058</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.594655031429463</v>
+        <v>2.552119703045374</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08639196192726784</v>
+        <v>0.08646979709933483</v>
       </c>
       <c r="C63">
-        <v>9.563626619119312</v>
+        <v>9.317691829849768</v>
       </c>
       <c r="D63">
-        <v>1.951326619119311</v>
+        <v>1.951091829849767</v>
       </c>
       <c r="E63">
-        <v>6.3177</v>
+        <v>6.5634</v>
       </c>
       <c r="F63">
-        <v>14.9877</v>
+        <v>15.2334</v>
       </c>
       <c r="G63">
         <v>22.6</v>
@@ -6566,28 +6566,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M63">
-        <v>1.07761563</v>
+        <v>1.09528146</v>
       </c>
       <c r="N63">
-        <v>1.672588451632653</v>
+        <v>1.654922621632654</v>
       </c>
       <c r="O63">
-        <v>0.2843400367775511</v>
+        <v>0.2813368456775511</v>
       </c>
       <c r="P63">
-        <v>1.388248414855102</v>
+        <v>1.373585775955102</v>
       </c>
       <c r="Q63">
-        <v>9.148248414855104</v>
+        <v>9.133585775955103</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1281769023776098</v>
+        <v>0.1301843607877232</v>
       </c>
       <c r="T63">
-        <v>1.902468877081058</v>
+        <v>1.948830503180675</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.552119703045374</v>
+        <v>2.510956482028513</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08646979709933483</v>
+        <v>0.08858694227140182</v>
       </c>
       <c r="C64">
-        <v>9.317691829849768</v>
+        <v>9.065627074937842</v>
       </c>
       <c r="D64">
-        <v>1.951091829849767</v>
+        <v>1.944727074937842</v>
       </c>
       <c r="E64">
-        <v>6.5634</v>
+        <v>6.809100000000001</v>
       </c>
       <c r="F64">
-        <v>15.2334</v>
+        <v>15.4791</v>
       </c>
       <c r="G64">
         <v>22.6</v>
@@ -6648,45 +6648,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M64">
-        <v>1.09528146</v>
+        <v>1.17331578</v>
       </c>
       <c r="N64">
-        <v>1.654922621632654</v>
+        <v>1.576888301632653</v>
       </c>
       <c r="O64">
-        <v>0.2813368456775511</v>
+        <v>0.2680710112775511</v>
       </c>
       <c r="P64">
-        <v>1.373585775955102</v>
+        <v>1.308817290355102</v>
       </c>
       <c r="Q64">
-        <v>9.133585775955103</v>
+        <v>9.068817290355103</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1301843607877232</v>
+        <v>0.1323003304632482</v>
       </c>
       <c r="T64">
-        <v>1.948830503180675</v>
+        <v>1.997698163123514</v>
       </c>
       <c r="U64">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.17</v>
       </c>
       <c r="W64">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.510956482028513</v>
+        <v>2.343958999368996</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08858694227140182</v>
+        <v>0.08869714744346881</v>
       </c>
       <c r="C65">
-        <v>9.065627074937842</v>
+        <v>8.819596902942967</v>
       </c>
       <c r="D65">
-        <v>1.944727074937842</v>
+        <v>1.944396902942967</v>
       </c>
       <c r="E65">
-        <v>6.809100000000001</v>
+        <v>7.0548</v>
       </c>
       <c r="F65">
-        <v>15.4791</v>
+        <v>15.7248</v>
       </c>
       <c r="G65">
         <v>22.6</v>
@@ -6730,28 +6730,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M65">
-        <v>1.17331578</v>
+        <v>1.19193984</v>
       </c>
       <c r="N65">
-        <v>1.576888301632653</v>
+        <v>1.558264241632654</v>
       </c>
       <c r="O65">
-        <v>0.2680710112775511</v>
+        <v>0.2649049210775511</v>
       </c>
       <c r="P65">
-        <v>1.308817290355102</v>
+        <v>1.293359320555102</v>
       </c>
       <c r="Q65">
-        <v>9.068817290355103</v>
+        <v>9.053359320555103</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1323003304632482</v>
+        <v>0.1345338540096356</v>
       </c>
       <c r="T65">
-        <v>1.997698163123514</v>
+        <v>2.049280693063178</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.343958999368996</v>
+        <v>2.307334640003856</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08869714744346881</v>
+        <v>0.0888073526155358</v>
       </c>
       <c r="C66">
-        <v>8.819596902942967</v>
+        <v>8.573566843040986</v>
       </c>
       <c r="D66">
-        <v>1.944396902942967</v>
+        <v>1.944066843040984</v>
       </c>
       <c r="E66">
-        <v>7.0548</v>
+        <v>7.300500000000001</v>
       </c>
       <c r="F66">
-        <v>15.7248</v>
+        <v>15.9705</v>
       </c>
       <c r="G66">
         <v>22.6</v>
@@ -6812,28 +6812,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M66">
-        <v>1.19193984</v>
+        <v>1.2105639</v>
       </c>
       <c r="N66">
-        <v>1.558264241632654</v>
+        <v>1.539640181632653</v>
       </c>
       <c r="O66">
-        <v>0.2649049210775511</v>
+        <v>0.2617388308775511</v>
       </c>
       <c r="P66">
-        <v>1.293359320555102</v>
+        <v>1.277901350755102</v>
       </c>
       <c r="Q66">
-        <v>9.053359320555103</v>
+        <v>9.037901350755103</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1345338540096356</v>
+        <v>0.1368950074729594</v>
       </c>
       <c r="T66">
-        <v>2.049280693063178</v>
+        <v>2.103810796142251</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.307334640003856</v>
+        <v>2.271837184003796</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0888073526155358</v>
+        <v>0.0889175577876028</v>
       </c>
       <c r="C67">
-        <v>8.573566843040986</v>
+        <v>8.32753689517482</v>
       </c>
       <c r="D67">
-        <v>1.944066843040984</v>
+        <v>1.94373689517482</v>
       </c>
       <c r="E67">
-        <v>7.300500000000001</v>
+        <v>7.546200000000001</v>
       </c>
       <c r="F67">
-        <v>15.9705</v>
+        <v>16.2162</v>
       </c>
       <c r="G67">
         <v>22.6</v>
@@ -6894,28 +6894,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M67">
-        <v>1.2105639</v>
+        <v>1.22918796</v>
       </c>
       <c r="N67">
-        <v>1.539640181632653</v>
+        <v>1.521016121632653</v>
       </c>
       <c r="O67">
-        <v>0.2617388308775511</v>
+        <v>0.2585727406775511</v>
       </c>
       <c r="P67">
-        <v>1.277901350755102</v>
+        <v>1.262443380955102</v>
       </c>
       <c r="Q67">
-        <v>9.037901350755103</v>
+        <v>9.022443380955103</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1368950074729594</v>
+        <v>0.1393950523164788</v>
       </c>
       <c r="T67">
-        <v>2.103810796142251</v>
+        <v>2.161548552343622</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.271837184003796</v>
+        <v>2.237415408488587</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0889175577876028</v>
+        <v>0.08902776295966978</v>
       </c>
       <c r="C68">
-        <v>8.32753689517482</v>
+        <v>8.081507059287443</v>
       </c>
       <c r="D68">
-        <v>1.94373689517482</v>
+        <v>1.943407059287441</v>
       </c>
       <c r="E68">
-        <v>7.546200000000001</v>
+        <v>7.7919</v>
       </c>
       <c r="F68">
-        <v>16.2162</v>
+        <v>16.4619</v>
       </c>
       <c r="G68">
         <v>22.6</v>
@@ -6976,28 +6976,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M68">
-        <v>1.22918796</v>
+        <v>1.24781202</v>
       </c>
       <c r="N68">
-        <v>1.521016121632653</v>
+        <v>1.502392061632654</v>
       </c>
       <c r="O68">
-        <v>0.2585727406775511</v>
+        <v>0.2554066504775511</v>
       </c>
       <c r="P68">
-        <v>1.262443380955102</v>
+        <v>1.246985411155102</v>
       </c>
       <c r="Q68">
-        <v>9.022443380955103</v>
+        <v>9.006985411155103</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1393950523164788</v>
+        <v>0.1420466150293024</v>
       </c>
       <c r="T68">
-        <v>2.161548552343622</v>
+        <v>2.222785566496591</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.237415408488587</v>
+        <v>2.2040211486604</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08902776295966978</v>
+        <v>0.08913796813173677</v>
       </c>
       <c r="C69">
-        <v>8.081507059287443</v>
+        <v>7.835477335321848</v>
       </c>
       <c r="D69">
-        <v>1.943407059287441</v>
+        <v>1.94307733532185</v>
       </c>
       <c r="E69">
-        <v>7.7919</v>
+        <v>8.037600000000003</v>
       </c>
       <c r="F69">
-        <v>16.4619</v>
+        <v>16.7076</v>
       </c>
       <c r="G69">
         <v>22.6</v>
@@ -7058,28 +7058,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M69">
-        <v>1.24781202</v>
+        <v>1.26643608</v>
       </c>
       <c r="N69">
-        <v>1.502392061632654</v>
+        <v>1.483768001632653</v>
       </c>
       <c r="O69">
-        <v>0.2554066504775511</v>
+        <v>0.2522405602775511</v>
       </c>
       <c r="P69">
-        <v>1.246985411155102</v>
+        <v>1.231527441355102</v>
       </c>
       <c r="Q69">
-        <v>9.006985411155103</v>
+        <v>8.991527441355103</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1420466150293024</v>
+        <v>0.1448639004116774</v>
       </c>
       <c r="T69">
-        <v>2.222785566496591</v>
+        <v>2.287849894034121</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.2040211486604</v>
+        <v>2.171609072944805</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08913796813173677</v>
+        <v>0.08924817330380377</v>
       </c>
       <c r="C70">
-        <v>7.835477335321848</v>
+        <v>7.589447723221088</v>
       </c>
       <c r="D70">
-        <v>1.94307733532185</v>
+        <v>1.942747723221089</v>
       </c>
       <c r="E70">
-        <v>8.037600000000003</v>
+        <v>8.283300000000002</v>
       </c>
       <c r="F70">
-        <v>16.7076</v>
+        <v>16.9533</v>
       </c>
       <c r="G70">
         <v>22.6</v>
@@ -7140,28 +7140,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M70">
-        <v>1.26643608</v>
+        <v>1.28506014</v>
       </c>
       <c r="N70">
-        <v>1.483768001632653</v>
+        <v>1.465143941632653</v>
       </c>
       <c r="O70">
-        <v>0.2522405602775511</v>
+        <v>0.2490744700775511</v>
       </c>
       <c r="P70">
-        <v>1.231527441355102</v>
+        <v>1.216069471555102</v>
       </c>
       <c r="Q70">
-        <v>8.991527441355103</v>
+        <v>8.976069471555103</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1448639004116774</v>
+        <v>0.1478629461413025</v>
       </c>
       <c r="T70">
-        <v>2.287849894034121</v>
+        <v>2.357111920122459</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.171609072944805</v>
+        <v>2.140136477684735</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08924817330380377</v>
+        <v>0.08935837847587075</v>
       </c>
       <c r="C71">
-        <v>7.589447723221088</v>
+        <v>7.343418222928243</v>
       </c>
       <c r="D71">
-        <v>1.942747723221089</v>
+        <v>1.942418222928242</v>
       </c>
       <c r="E71">
-        <v>8.283300000000002</v>
+        <v>8.529000000000002</v>
       </c>
       <c r="F71">
-        <v>16.9533</v>
+        <v>17.199</v>
       </c>
       <c r="G71">
         <v>22.6</v>
@@ -7222,28 +7222,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M71">
-        <v>1.28506014</v>
+        <v>1.3036842</v>
       </c>
       <c r="N71">
-        <v>1.465143941632653</v>
+        <v>1.446519881632653</v>
       </c>
       <c r="O71">
-        <v>0.2490744700775511</v>
+        <v>0.2459083798775511</v>
       </c>
       <c r="P71">
-        <v>1.216069471555102</v>
+        <v>1.200611501755102</v>
       </c>
       <c r="Q71">
-        <v>8.976069471555103</v>
+        <v>8.960611501755103</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1478629461413025</v>
+        <v>0.1510619282529025</v>
       </c>
       <c r="T71">
-        <v>2.357111920122459</v>
+        <v>2.430991414616687</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.140136477684735</v>
+        <v>2.109563099432097</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08935837847587075</v>
+        <v>0.08946858364793775</v>
       </c>
       <c r="C72">
-        <v>7.343418222928243</v>
+        <v>7.097388834386429</v>
       </c>
       <c r="D72">
-        <v>1.942418222928242</v>
+        <v>1.942088834386427</v>
       </c>
       <c r="E72">
-        <v>8.529000000000002</v>
+        <v>8.774700000000001</v>
       </c>
       <c r="F72">
-        <v>17.199</v>
+        <v>17.4447</v>
       </c>
       <c r="G72">
         <v>22.6</v>
@@ -7304,28 +7304,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M72">
-        <v>1.3036842</v>
+        <v>1.32230826</v>
       </c>
       <c r="N72">
-        <v>1.446519881632653</v>
+        <v>1.427895821632653</v>
       </c>
       <c r="O72">
-        <v>0.2459083798775511</v>
+        <v>0.2427422896775511</v>
       </c>
       <c r="P72">
-        <v>1.200611501755102</v>
+        <v>1.185153531955102</v>
       </c>
       <c r="Q72">
-        <v>8.960611501755103</v>
+        <v>8.945153531955103</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1510619282529025</v>
+        <v>0.154481529820475</v>
       </c>
       <c r="T72">
-        <v>2.430991414616687</v>
+        <v>2.509966046662241</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.109563099432097</v>
+        <v>2.079850943102067</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08946858364793775</v>
+        <v>0.08957878882000474</v>
       </c>
       <c r="C73">
-        <v>7.097388834386429</v>
+        <v>6.851359557538803</v>
       </c>
       <c r="D73">
-        <v>1.942088834386427</v>
+        <v>1.941759557538803</v>
       </c>
       <c r="E73">
-        <v>8.774700000000001</v>
+        <v>9.0204</v>
       </c>
       <c r="F73">
-        <v>17.4447</v>
+        <v>17.6904</v>
       </c>
       <c r="G73">
         <v>22.6</v>
@@ -7386,28 +7386,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M73">
-        <v>1.32230826</v>
+        <v>1.34093232</v>
       </c>
       <c r="N73">
-        <v>1.427895821632653</v>
+        <v>1.409271761632654</v>
       </c>
       <c r="O73">
-        <v>0.2427422896775511</v>
+        <v>0.2395761994775511</v>
       </c>
       <c r="P73">
-        <v>1.185153531955102</v>
+        <v>1.169695562155102</v>
       </c>
       <c r="Q73">
-        <v>8.945153531955103</v>
+        <v>8.929695562155104</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.154481529820475</v>
+        <v>0.1581453886428741</v>
       </c>
       <c r="T73">
-        <v>2.50996604666224</v>
+        <v>2.594581723853905</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.079850943102067</v>
+        <v>2.050964124447872</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08957878882000474</v>
+        <v>0.08968899399207172</v>
       </c>
       <c r="C74">
-        <v>6.851359557538803</v>
+        <v>6.605330392328568</v>
       </c>
       <c r="D74">
-        <v>1.941759557538803</v>
+        <v>1.941430392328567</v>
       </c>
       <c r="E74">
-        <v>9.0204</v>
+        <v>9.2661</v>
       </c>
       <c r="F74">
-        <v>17.6904</v>
+        <v>17.9361</v>
       </c>
       <c r="G74">
         <v>22.6</v>
@@ -7468,28 +7468,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M74">
-        <v>1.34093232</v>
+        <v>1.35955638</v>
       </c>
       <c r="N74">
-        <v>1.409271761632654</v>
+        <v>1.390647701632653</v>
       </c>
       <c r="O74">
-        <v>0.2395761994775511</v>
+        <v>0.2364101092775511</v>
       </c>
       <c r="P74">
-        <v>1.169695562155102</v>
+        <v>1.154237592355102</v>
       </c>
       <c r="Q74">
-        <v>8.929695562155104</v>
+        <v>8.914237592355104</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1581453886428741</v>
+        <v>0.1620806444150805</v>
       </c>
       <c r="T74">
-        <v>2.594581723853905</v>
+        <v>2.685465228985692</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.050964124447872</v>
+        <v>2.022868725482832</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08968899399207172</v>
+        <v>0.09852083916413872</v>
       </c>
       <c r="C75">
-        <v>6.605330392328568</v>
+        <v>6.333609062684854</v>
       </c>
       <c r="D75">
-        <v>1.941430392328567</v>
+        <v>1.91540906268485</v>
       </c>
       <c r="E75">
-        <v>9.2661</v>
+        <v>9.511799999999999</v>
       </c>
       <c r="F75">
-        <v>17.9361</v>
+        <v>18.1818</v>
       </c>
       <c r="G75">
         <v>22.6</v>
@@ -7550,45 +7550,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M75">
-        <v>1.35955638</v>
+        <v>1.636362</v>
       </c>
       <c r="N75">
-        <v>1.390647701632653</v>
+        <v>1.113842081632654</v>
       </c>
       <c r="O75">
-        <v>0.2364101092775511</v>
+        <v>0.1893531538775511</v>
       </c>
       <c r="P75">
-        <v>1.154237592355102</v>
+        <v>0.9244889277551026</v>
       </c>
       <c r="Q75">
-        <v>8.914237592355104</v>
+        <v>8.684488927755103</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1620806444150805</v>
+        <v>0.1663186121697643</v>
       </c>
       <c r="T75">
-        <v>2.685465228985692</v>
+        <v>2.783339772973772</v>
       </c>
       <c r="U75">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.17</v>
       </c>
       <c r="W75">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.022868725482832</v>
+        <v>1.680681952790797</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09852083916413872</v>
+        <v>0.0987489043362057</v>
       </c>
       <c r="C76">
-        <v>6.333609062684854</v>
+        <v>6.087246348246715</v>
       </c>
       <c r="D76">
-        <v>1.91540906268485</v>
+        <v>1.914746348246717</v>
       </c>
       <c r="E76">
-        <v>9.511799999999999</v>
+        <v>9.757500000000002</v>
       </c>
       <c r="F76">
-        <v>18.1818</v>
+        <v>18.4275</v>
       </c>
       <c r="G76">
         <v>22.6</v>
@@ -7632,28 +7632,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M76">
-        <v>1.636362</v>
+        <v>1.658475</v>
       </c>
       <c r="N76">
-        <v>1.113842081632654</v>
+        <v>1.091729081632653</v>
       </c>
       <c r="O76">
-        <v>0.1893531538775511</v>
+        <v>0.1855939438775511</v>
       </c>
       <c r="P76">
-        <v>0.9244889277551026</v>
+        <v>0.9061351377551023</v>
       </c>
       <c r="Q76">
-        <v>8.684488927755103</v>
+        <v>8.666135137755102</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1663186121697643</v>
+        <v>0.1708956173448229</v>
       </c>
       <c r="T76">
-        <v>2.783339772973772</v>
+        <v>2.889044280480898</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.680681952790797</v>
+        <v>1.658272860086919</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0987489043362057</v>
+        <v>0.0989769695082727</v>
       </c>
       <c r="C77">
-        <v>6.087246348246715</v>
+        <v>5.840884092236532</v>
       </c>
       <c r="D77">
-        <v>1.914746348246717</v>
+        <v>1.914084092236532</v>
       </c>
       <c r="E77">
-        <v>9.757500000000002</v>
+        <v>10.0032</v>
       </c>
       <c r="F77">
-        <v>18.4275</v>
+        <v>18.6732</v>
       </c>
       <c r="G77">
         <v>22.6</v>
@@ -7714,28 +7714,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M77">
-        <v>1.658475</v>
+        <v>1.680588</v>
       </c>
       <c r="N77">
-        <v>1.091729081632653</v>
+        <v>1.069616081632654</v>
       </c>
       <c r="O77">
-        <v>0.1855939438775511</v>
+        <v>0.1818347338775511</v>
       </c>
       <c r="P77">
-        <v>0.9061351377551023</v>
+        <v>0.8877813477551025</v>
       </c>
       <c r="Q77">
-        <v>8.666135137755102</v>
+        <v>8.647781347755103</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1708956173448229</v>
+        <v>0.175854039617803</v>
       </c>
       <c r="T77">
-        <v>2.889044280480898</v>
+        <v>3.003557496946951</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.658272860086919</v>
+        <v>1.636453480348934</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0989769695082727</v>
+        <v>0.0992050346803397</v>
       </c>
       <c r="C78">
-        <v>5.840884092236532</v>
+        <v>5.594522294178788</v>
       </c>
       <c r="D78">
-        <v>1.914084092236532</v>
+        <v>1.913422294178787</v>
       </c>
       <c r="E78">
-        <v>10.0032</v>
+        <v>10.2489</v>
       </c>
       <c r="F78">
-        <v>18.6732</v>
+        <v>18.9189</v>
       </c>
       <c r="G78">
         <v>22.6</v>
@@ -7796,28 +7796,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M78">
-        <v>1.680588</v>
+        <v>1.702701</v>
       </c>
       <c r="N78">
-        <v>1.069616081632654</v>
+        <v>1.047503081632654</v>
       </c>
       <c r="O78">
-        <v>0.1818347338775511</v>
+        <v>0.1780755238775511</v>
       </c>
       <c r="P78">
-        <v>0.8877813477551025</v>
+        <v>0.8694275577551025</v>
       </c>
       <c r="Q78">
-        <v>8.647781347755103</v>
+        <v>8.629427557755104</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.175854039617803</v>
+        <v>0.1812436290449552</v>
       </c>
       <c r="T78">
-        <v>3.003557496946951</v>
+        <v>3.128028384410051</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.636453480348934</v>
+        <v>1.615200837747</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0992050346803397</v>
+        <v>0.09943309985240668</v>
       </c>
       <c r="C79">
-        <v>5.594522294178788</v>
+        <v>5.348160953598637</v>
       </c>
       <c r="D79">
-        <v>1.913422294178787</v>
+        <v>1.912760953598635</v>
       </c>
       <c r="E79">
-        <v>10.2489</v>
+        <v>10.4946</v>
       </c>
       <c r="F79">
-        <v>18.9189</v>
+        <v>19.1646</v>
       </c>
       <c r="G79">
         <v>22.6</v>
@@ -7878,28 +7878,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M79">
-        <v>1.702701</v>
+        <v>1.724814</v>
       </c>
       <c r="N79">
-        <v>1.047503081632654</v>
+        <v>1.025390081632654</v>
       </c>
       <c r="O79">
-        <v>0.1780755238775511</v>
+        <v>0.1743163138775511</v>
       </c>
       <c r="P79">
-        <v>0.8694275577551025</v>
+        <v>0.8510737677551026</v>
       </c>
       <c r="Q79">
-        <v>8.629427557755104</v>
+        <v>8.611073767755103</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1812436290449552</v>
+        <v>0.1871231811473032</v>
       </c>
       <c r="T79">
-        <v>3.128028384410051</v>
+        <v>3.263814807097071</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.615200837747</v>
+        <v>1.594493134698961</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09943309985240668</v>
+        <v>0.09966116502447367</v>
       </c>
       <c r="C80">
-        <v>5.348160953598637</v>
+        <v>5.101800070021884</v>
       </c>
       <c r="D80">
-        <v>1.912760953598635</v>
+        <v>1.912100070021881</v>
       </c>
       <c r="E80">
-        <v>10.4946</v>
+        <v>10.7403</v>
       </c>
       <c r="F80">
-        <v>19.1646</v>
+        <v>19.4103</v>
       </c>
       <c r="G80">
         <v>22.6</v>
@@ -7960,28 +7960,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M80">
-        <v>1.724814</v>
+        <v>1.746927</v>
       </c>
       <c r="N80">
-        <v>1.025390081632654</v>
+        <v>1.003277081632654</v>
       </c>
       <c r="O80">
-        <v>0.1743163138775511</v>
+        <v>0.1705571038775512</v>
       </c>
       <c r="P80">
-        <v>0.8510737677551026</v>
+        <v>0.8327199777551025</v>
       </c>
       <c r="Q80">
-        <v>8.611073767755103</v>
+        <v>8.592719977755102</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1871231811473032</v>
+        <v>0.1935626905927318</v>
       </c>
       <c r="T80">
-        <v>3.263814807097071</v>
+        <v>3.412533270039996</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.594493134698961</v>
+        <v>1.574309677297708</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09966116502447367</v>
+        <v>0.09988923019654067</v>
       </c>
       <c r="C81">
-        <v>5.101800070021884</v>
+        <v>4.855439642974986</v>
       </c>
       <c r="D81">
-        <v>1.912100070021881</v>
+        <v>1.911439642974987</v>
       </c>
       <c r="E81">
-        <v>10.7403</v>
+        <v>10.986</v>
       </c>
       <c r="F81">
-        <v>19.4103</v>
+        <v>19.656</v>
       </c>
       <c r="G81">
         <v>22.6</v>
@@ -8042,28 +8042,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M81">
-        <v>1.746927</v>
+        <v>1.76904</v>
       </c>
       <c r="N81">
-        <v>1.003277081632654</v>
+        <v>0.9811640816326535</v>
       </c>
       <c r="O81">
-        <v>0.1705571038775512</v>
+        <v>0.1667978938775511</v>
       </c>
       <c r="P81">
-        <v>0.8327199777551025</v>
+        <v>0.8143661877551024</v>
       </c>
       <c r="Q81">
-        <v>8.592719977755102</v>
+        <v>8.574366187755103</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1935626905927318</v>
+        <v>0.2006461509827034</v>
       </c>
       <c r="T81">
-        <v>3.412533270039996</v>
+        <v>3.576123579277215</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.574309677297708</v>
+        <v>1.554630806331487</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09988923019654067</v>
+        <v>0.1001172953686077</v>
       </c>
       <c r="C82">
-        <v>4.855439642974986</v>
+        <v>4.609079671985068</v>
       </c>
       <c r="D82">
-        <v>1.911439642974987</v>
+        <v>1.910779671985069</v>
       </c>
       <c r="E82">
-        <v>10.986</v>
+        <v>11.2317</v>
       </c>
       <c r="F82">
-        <v>19.656</v>
+        <v>19.9017</v>
       </c>
       <c r="G82">
         <v>22.6</v>
@@ -8124,28 +8124,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M82">
-        <v>1.76904</v>
+        <v>1.791153</v>
       </c>
       <c r="N82">
-        <v>0.9811640816326535</v>
+        <v>0.9590510816326536</v>
       </c>
       <c r="O82">
-        <v>0.1667978938775511</v>
+        <v>0.1630386838775511</v>
       </c>
       <c r="P82">
-        <v>0.8143661877551024</v>
+        <v>0.7960123977551025</v>
       </c>
       <c r="Q82">
-        <v>8.574366187755103</v>
+        <v>8.556012397755103</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2006461509827034</v>
+        <v>0.2084752387821457</v>
       </c>
       <c r="T82">
-        <v>3.576123579277215</v>
+        <v>3.75693392106572</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.554630806331487</v>
+        <v>1.535437833413814</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1001172953686077</v>
+        <v>0.1003453605406747</v>
       </c>
       <c r="C83">
-        <v>4.609079671985068</v>
+        <v>4.362720156579897</v>
       </c>
       <c r="D83">
-        <v>1.910779671985069</v>
+        <v>1.910120156579897</v>
       </c>
       <c r="E83">
-        <v>11.2317</v>
+        <v>11.4774</v>
       </c>
       <c r="F83">
-        <v>19.9017</v>
+        <v>20.1474</v>
       </c>
       <c r="G83">
         <v>22.6</v>
@@ -8206,28 +8206,28 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M83">
-        <v>1.791153</v>
+        <v>1.813266</v>
       </c>
       <c r="N83">
-        <v>0.9590510816326536</v>
+        <v>0.9369380816326536</v>
       </c>
       <c r="O83">
-        <v>0.1630386838775511</v>
+        <v>0.1592794738775511</v>
       </c>
       <c r="P83">
-        <v>0.7960123977551025</v>
+        <v>0.7776586077551024</v>
       </c>
       <c r="Q83">
-        <v>8.556012397755103</v>
+        <v>8.537658607755104</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2084752387821457</v>
+        <v>0.2171742252259704</v>
       </c>
       <c r="T83">
-        <v>3.75693392106572</v>
+        <v>3.957834300830725</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.535437833413814</v>
+        <v>1.516712981786816</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1003453605406747</v>
+        <v>0.1417991203962972</v>
       </c>
       <c r="C84">
-        <v>4.362720156579897</v>
+        <v>4.004260319508777</v>
       </c>
       <c r="D84">
-        <v>1.910120156579897</v>
+        <v>1.797360319508776</v>
       </c>
       <c r="E84">
-        <v>11.4774</v>
+        <v>11.7231</v>
       </c>
       <c r="F84">
-        <v>20.1474</v>
+        <v>20.3931</v>
       </c>
       <c r="G84">
         <v>22.6</v>
@@ -8288,45 +8288,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M84">
-        <v>1.813266</v>
+        <v>2.993707080000001</v>
       </c>
       <c r="N84">
-        <v>0.9369380816326536</v>
+        <v>-0.2435029983673469</v>
       </c>
       <c r="O84">
-        <v>0.1592794738775511</v>
+        <v>-0.04139550972244898</v>
       </c>
       <c r="P84">
-        <v>0.7776586077551024</v>
+        <v>-0.2021074886448979</v>
       </c>
       <c r="Q84">
-        <v>8.537658607755104</v>
+        <v>7.557892511355103</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2171742252259704</v>
+        <v>0.2293164792105565</v>
       </c>
       <c r="T84">
-        <v>3.957834300830725</v>
+        <v>4.238255870913545</v>
       </c>
       <c r="U84">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.17</v>
+        <v>0.1561724916245149</v>
       </c>
       <c r="W84">
-        <v>0.07469999999999999</v>
+        <v>0.1238738782295212</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.516712981786816</v>
+        <v>0.9186617154383231</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1417991203962972</v>
+        <v>0.1428091203962972</v>
       </c>
       <c r="C85">
-        <v>4.004260319508777</v>
+        <v>3.75597887883368</v>
       </c>
       <c r="D85">
-        <v>1.797360319508776</v>
+        <v>1.794778878833684</v>
       </c>
       <c r="E85">
-        <v>11.7231</v>
+        <v>11.9688</v>
       </c>
       <c r="F85">
-        <v>20.3931</v>
+        <v>20.6388</v>
       </c>
       <c r="G85">
         <v>22.6</v>
@@ -8370,37 +8370,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M85">
-        <v>2.993707080000001</v>
+        <v>3.029775840000001</v>
       </c>
       <c r="N85">
-        <v>-0.2435029983673469</v>
+        <v>-0.2795717583673474</v>
       </c>
       <c r="O85">
-        <v>-0.04139550972244898</v>
+        <v>-0.04752719892244905</v>
       </c>
       <c r="P85">
-        <v>-0.2021074886448979</v>
+        <v>-0.2320445594448983</v>
       </c>
       <c r="Q85">
-        <v>7.557892511355103</v>
+        <v>7.527955440555102</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2293164792105565</v>
+        <v>0.2407862591612163</v>
       </c>
       <c r="T85">
-        <v>4.238255870913545</v>
+        <v>4.503146862845643</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1561724916245149</v>
+        <v>0.1543132952956517</v>
       </c>
       <c r="W85">
-        <v>0.1238738782295212</v>
+        <v>0.1241468082505984</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9186617154383231</v>
+        <v>0.9077252664450096</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1428091203962972</v>
+        <v>0.1438191203962972</v>
       </c>
       <c r="C86">
-        <v>3.755978878833684</v>
+        <v>3.507704842660345</v>
       </c>
       <c r="D86">
-        <v>1.794778878833684</v>
+        <v>1.792204842660344</v>
       </c>
       <c r="E86">
-        <v>11.9688</v>
+        <v>12.2145</v>
       </c>
       <c r="F86">
-        <v>20.6388</v>
+        <v>20.8845</v>
       </c>
       <c r="G86">
         <v>22.6</v>
@@ -8452,37 +8452,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M86">
-        <v>3.02977584</v>
+        <v>3.0658446</v>
       </c>
       <c r="N86">
-        <v>-0.2795717583673465</v>
+        <v>-0.3156405183673465</v>
       </c>
       <c r="O86">
-        <v>-0.04752719892244891</v>
+        <v>-0.05365888812244891</v>
       </c>
       <c r="P86">
-        <v>-0.2320445594448976</v>
+        <v>-0.2619816302448976</v>
       </c>
       <c r="Q86">
-        <v>7.527955440555103</v>
+        <v>7.498018369755103</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2407862591612162</v>
+        <v>0.2537853431052973</v>
       </c>
       <c r="T86">
-        <v>4.50314686284564</v>
+        <v>4.803356653702016</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1543132952956517</v>
+        <v>0.1524978447627617</v>
       </c>
       <c r="W86">
-        <v>0.1241468082505984</v>
+        <v>0.1244133163888266</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9077252664450098</v>
+        <v>0.8970461456633039</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1438191203962972</v>
+        <v>0.1448291203962972</v>
       </c>
       <c r="C87">
-        <v>3.507704842660345</v>
+        <v>3.259438179176218</v>
       </c>
       <c r="D87">
-        <v>1.792204842660344</v>
+        <v>1.789638179176214</v>
       </c>
       <c r="E87">
-        <v>12.2145</v>
+        <v>12.4602</v>
       </c>
       <c r="F87">
-        <v>20.8845</v>
+        <v>21.1302</v>
       </c>
       <c r="G87">
         <v>22.6</v>
@@ -8534,37 +8534,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M87">
-        <v>3.0658446</v>
+        <v>3.10191336</v>
       </c>
       <c r="N87">
-        <v>-0.3156405183673465</v>
+        <v>-0.3517092783673466</v>
       </c>
       <c r="O87">
-        <v>-0.05365888812244891</v>
+        <v>-0.05979057732244892</v>
       </c>
       <c r="P87">
-        <v>-0.2619816302448976</v>
+        <v>-0.2919187010448976</v>
       </c>
       <c r="Q87">
-        <v>7.498018369755103</v>
+        <v>7.468081298955103</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2537853431052973</v>
+        <v>0.26864143904139</v>
       </c>
       <c r="T87">
-        <v>4.803356653702016</v>
+        <v>5.146453557537875</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1524978447627617</v>
+        <v>0.1507246140097063</v>
       </c>
       <c r="W87">
-        <v>0.1244133163888266</v>
+        <v>0.1246736266633751</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8970461456633039</v>
+        <v>0.8866153765276841</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1448291203962972</v>
+        <v>0.1458391203962972</v>
       </c>
       <c r="C88">
-        <v>3.259438179176218</v>
+        <v>3.011178856750728</v>
       </c>
       <c r="D88">
-        <v>1.789638179176214</v>
+        <v>1.78707885675073</v>
       </c>
       <c r="E88">
-        <v>12.4602</v>
+        <v>12.7059</v>
       </c>
       <c r="F88">
-        <v>21.1302</v>
+        <v>21.3759</v>
       </c>
       <c r="G88">
         <v>22.6</v>
@@ -8616,37 +8616,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M88">
-        <v>3.10191336</v>
+        <v>3.137982120000001</v>
       </c>
       <c r="N88">
-        <v>-0.3517092783673466</v>
+        <v>-0.387778038367347</v>
       </c>
       <c r="O88">
-        <v>-0.05979057732244892</v>
+        <v>-0.06592226652244899</v>
       </c>
       <c r="P88">
-        <v>-0.2919187010448976</v>
+        <v>-0.3218557718448981</v>
       </c>
       <c r="Q88">
-        <v>7.468081298955103</v>
+        <v>7.438144228155102</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.26864143904139</v>
+        <v>0.2857830881984199</v>
       </c>
       <c r="T88">
-        <v>5.146453557537875</v>
+        <v>5.542334600425403</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1507246140097063</v>
+        <v>0.1489921471820085</v>
       </c>
       <c r="W88">
-        <v>0.1246736266633751</v>
+        <v>0.1249279527936812</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8866153765276841</v>
+        <v>0.8764243951882852</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1458391203962972</v>
+        <v>0.1468491203962972</v>
       </c>
       <c r="C89">
-        <v>3.011178856750728</v>
+        <v>2.762926843934004</v>
       </c>
       <c r="D89">
-        <v>1.78707885675073</v>
+        <v>1.784526843934004</v>
       </c>
       <c r="E89">
-        <v>12.7059</v>
+        <v>12.9516</v>
       </c>
       <c r="F89">
-        <v>21.3759</v>
+        <v>21.6216</v>
       </c>
       <c r="G89">
         <v>22.6</v>
@@ -8698,37 +8698,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M89">
-        <v>3.137982120000001</v>
+        <v>3.17405088</v>
       </c>
       <c r="N89">
-        <v>-0.387778038367347</v>
+        <v>-0.4238467983673466</v>
       </c>
       <c r="O89">
-        <v>-0.06592226652244899</v>
+        <v>-0.07205395572244894</v>
       </c>
       <c r="P89">
-        <v>-0.3218557718448981</v>
+        <v>-0.3517928426448977</v>
       </c>
       <c r="Q89">
-        <v>7.438144228155102</v>
+        <v>7.408207157355103</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2857830881984199</v>
+        <v>0.3057816788816217</v>
       </c>
       <c r="T89">
-        <v>5.542334600425403</v>
+        <v>6.004195817127521</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1489921471820085</v>
+        <v>0.1472990546003948</v>
       </c>
       <c r="W89">
-        <v>0.1249279527936812</v>
+        <v>0.1251764987846621</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8764243951882852</v>
+        <v>0.8664650270611457</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1468491203962972</v>
+        <v>0.1478591203962972</v>
       </c>
       <c r="C90">
-        <v>2.762926843934004</v>
+        <v>2.514682109455542</v>
       </c>
       <c r="D90">
-        <v>1.784526843934004</v>
+        <v>1.781982109455541</v>
       </c>
       <c r="E90">
-        <v>12.9516</v>
+        <v>13.1973</v>
       </c>
       <c r="F90">
-        <v>21.6216</v>
+        <v>21.8673</v>
       </c>
       <c r="G90">
         <v>22.6</v>
@@ -8780,37 +8780,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M90">
-        <v>3.17405088</v>
+        <v>3.21011964</v>
       </c>
       <c r="N90">
-        <v>-0.4238467983673466</v>
+        <v>-0.4599155583673467</v>
       </c>
       <c r="O90">
-        <v>-0.07205395572244894</v>
+        <v>-0.07818564492244894</v>
       </c>
       <c r="P90">
-        <v>-0.3517928426448977</v>
+        <v>-0.3817299134448977</v>
       </c>
       <c r="Q90">
-        <v>7.408207157355103</v>
+        <v>7.378270086555103</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3057816788816217</v>
+        <v>0.3294163769617691</v>
       </c>
       <c r="T90">
-        <v>6.004195817127521</v>
+        <v>6.550031800502751</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1472990546003948</v>
+        <v>0.145644009043087</v>
       </c>
       <c r="W90">
-        <v>0.1251764987846621</v>
+        <v>0.1254194594724748</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8664650270611457</v>
+        <v>0.8567294649593351</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1478591203962972</v>
+        <v>0.1488691203962972</v>
       </c>
       <c r="C91">
-        <v>2.514682109455542</v>
+        <v>2.266444622222959</v>
       </c>
       <c r="D91">
-        <v>1.781982109455541</v>
+        <v>1.779444622222957</v>
       </c>
       <c r="E91">
-        <v>13.1973</v>
+        <v>13.443</v>
       </c>
       <c r="F91">
-        <v>21.8673</v>
+        <v>22.113</v>
       </c>
       <c r="G91">
         <v>22.6</v>
@@ -8862,37 +8862,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M91">
-        <v>3.21011964</v>
+        <v>3.2461884</v>
       </c>
       <c r="N91">
-        <v>-0.4599155583673467</v>
+        <v>-0.4959843183673467</v>
       </c>
       <c r="O91">
-        <v>-0.07818564492244894</v>
+        <v>-0.08431733412244895</v>
       </c>
       <c r="P91">
-        <v>-0.3817299134448977</v>
+        <v>-0.4116669842448977</v>
       </c>
       <c r="Q91">
-        <v>7.378270086555103</v>
+        <v>7.348333015755103</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3294163769617691</v>
+        <v>0.357778014657946</v>
       </c>
       <c r="T91">
-        <v>6.550031800502751</v>
+        <v>7.205034980553026</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.145644009043087</v>
+        <v>0.1440257422759416</v>
       </c>
       <c r="W91">
-        <v>0.1254194594724748</v>
+        <v>0.1256570210338918</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8567294649593351</v>
+        <v>0.8472102486820091</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1488691203962972</v>
+        <v>0.1498791203962972</v>
       </c>
       <c r="C92">
-        <v>2.266444622222959</v>
+        <v>2.018214351320712</v>
       </c>
       <c r="D92">
-        <v>1.779444622222957</v>
+        <v>1.776914351320714</v>
       </c>
       <c r="E92">
-        <v>13.443</v>
+        <v>13.6887</v>
       </c>
       <c r="F92">
-        <v>22.113</v>
+        <v>22.3587</v>
       </c>
       <c r="G92">
         <v>22.6</v>
@@ -8944,37 +8944,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M92">
-        <v>3.2461884</v>
+        <v>3.282257160000001</v>
       </c>
       <c r="N92">
-        <v>-0.4959843183673467</v>
+        <v>-0.5320530783673472</v>
       </c>
       <c r="O92">
-        <v>-0.08431733412244895</v>
+        <v>-0.09044902332244903</v>
       </c>
       <c r="P92">
-        <v>-0.4116669842448977</v>
+        <v>-0.4416040550448981</v>
       </c>
       <c r="Q92">
-        <v>7.348333015755103</v>
+        <v>7.318395944955102</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.357778014657946</v>
+        <v>0.3924422385088289</v>
       </c>
       <c r="T92">
-        <v>7.205034980553026</v>
+        <v>8.005594422836696</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1440257422759416</v>
+        <v>0.1424430418113708</v>
       </c>
       <c r="W92">
-        <v>0.1256570210338918</v>
+        <v>0.1258893614620908</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8472102486820091</v>
+        <v>0.8379002459492397</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1498791203962972</v>
+        <v>0.1508891203962972</v>
       </c>
       <c r="C93">
-        <v>2.018214351320712</v>
+        <v>1.769991266008866</v>
       </c>
       <c r="D93">
-        <v>1.776914351320714</v>
+        <v>1.774391266008867</v>
       </c>
       <c r="E93">
-        <v>13.6887</v>
+        <v>13.9344</v>
       </c>
       <c r="F93">
-        <v>22.3587</v>
+        <v>22.6044</v>
       </c>
       <c r="G93">
         <v>22.6</v>
@@ -9026,37 +9026,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M93">
-        <v>3.282257160000001</v>
+        <v>3.31832592</v>
       </c>
       <c r="N93">
-        <v>-0.5320530783673472</v>
+        <v>-0.5681218383673468</v>
       </c>
       <c r="O93">
-        <v>-0.09044902332244903</v>
+        <v>-0.09658071252244896</v>
       </c>
       <c r="P93">
-        <v>-0.4416040550448981</v>
+        <v>-0.4715411258448978</v>
       </c>
       <c r="Q93">
-        <v>7.318395944955102</v>
+        <v>7.288458874155102</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3924422385088289</v>
+        <v>0.4357725183224327</v>
       </c>
       <c r="T93">
-        <v>8.005594422836696</v>
+        <v>9.006293725691286</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1424430418113708</v>
+        <v>0.1408947478786385</v>
       </c>
       <c r="W93">
-        <v>0.1258893614620908</v>
+        <v>0.1261166510114159</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8379002459492397</v>
+        <v>0.8287926345802263</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1508891203962972</v>
+        <v>0.1518991203962972</v>
       </c>
       <c r="C94">
-        <v>1.769991266008866</v>
+        <v>1.521775335721816</v>
       </c>
       <c r="D94">
-        <v>1.774391266008867</v>
+        <v>1.771875335721816</v>
       </c>
       <c r="E94">
-        <v>13.9344</v>
+        <v>14.1801</v>
       </c>
       <c r="F94">
-        <v>22.6044</v>
+        <v>22.8501</v>
       </c>
       <c r="G94">
         <v>22.6</v>
@@ -9108,37 +9108,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M94">
-        <v>3.31832592</v>
+        <v>3.35439468</v>
       </c>
       <c r="N94">
-        <v>-0.5681218383673468</v>
+        <v>-0.6041905983673468</v>
       </c>
       <c r="O94">
-        <v>-0.09658071252244896</v>
+        <v>-0.102712401722449</v>
       </c>
       <c r="P94">
-        <v>-0.4715411258448978</v>
+        <v>-0.5014781966448978</v>
       </c>
       <c r="Q94">
-        <v>7.288458874155102</v>
+        <v>7.258521803355103</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4357725183224327</v>
+        <v>0.4914828780827802</v>
       </c>
       <c r="T94">
-        <v>9.006293725691286</v>
+        <v>10.29290711507576</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1408947478786385</v>
+        <v>0.1393797505896209</v>
       </c>
       <c r="W94">
-        <v>0.1261166510114159</v>
+        <v>0.1263390526134437</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8287926345802263</v>
+        <v>0.8198808858212991</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1518991203962972</v>
+        <v>0.1529091203962972</v>
       </c>
       <c r="C95">
-        <v>1.521775335721816</v>
+        <v>1.273566530067072</v>
       </c>
       <c r="D95">
-        <v>1.771875335721816</v>
+        <v>1.769366530067072</v>
       </c>
       <c r="E95">
-        <v>14.1801</v>
+        <v>14.4258</v>
       </c>
       <c r="F95">
-        <v>22.8501</v>
+        <v>23.0958</v>
       </c>
       <c r="G95">
         <v>22.6</v>
@@ -9190,37 +9190,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M95">
-        <v>3.35439468</v>
+        <v>3.39046344</v>
       </c>
       <c r="N95">
-        <v>-0.6041905983673468</v>
+        <v>-0.6402593583673468</v>
       </c>
       <c r="O95">
-        <v>-0.102712401722449</v>
+        <v>-0.108844090922449</v>
       </c>
       <c r="P95">
-        <v>-0.5014781966448978</v>
+        <v>-0.5314152674448979</v>
       </c>
       <c r="Q95">
-        <v>7.258521803355103</v>
+        <v>7.228584732555102</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4914828780827802</v>
+        <v>0.5657633577632437</v>
       </c>
       <c r="T95">
-        <v>10.29290711507576</v>
+        <v>12.00839163425505</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1393797505896209</v>
+        <v>0.1378969872854759</v>
       </c>
       <c r="W95">
-        <v>0.1263390526134437</v>
+        <v>0.1265567222664921</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8198808858212991</v>
+        <v>0.8111587487380938</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1529091203962972</v>
+        <v>0.1539191203962972</v>
       </c>
       <c r="C96">
-        <v>1.273566530067072</v>
+        <v>1.025364818824034</v>
       </c>
       <c r="D96">
-        <v>1.769366530067072</v>
+        <v>1.766864818824037</v>
       </c>
       <c r="E96">
-        <v>14.4258</v>
+        <v>14.6715</v>
       </c>
       <c r="F96">
-        <v>23.0958</v>
+        <v>23.3415</v>
       </c>
       <c r="G96">
         <v>22.6</v>
@@ -9272,37 +9272,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M96">
-        <v>3.39046344</v>
+        <v>3.426532200000001</v>
       </c>
       <c r="N96">
-        <v>-0.6402593583673468</v>
+        <v>-0.6763281183673473</v>
       </c>
       <c r="O96">
-        <v>-0.108844090922449</v>
+        <v>-0.1149757801224491</v>
       </c>
       <c r="P96">
-        <v>-0.5314152674448979</v>
+        <v>-0.5613523382448983</v>
       </c>
       <c r="Q96">
-        <v>7.228584732555102</v>
+        <v>7.198647661755103</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5657633577632437</v>
+        <v>0.6697560293158927</v>
       </c>
       <c r="T96">
-        <v>12.00839163425505</v>
+        <v>14.41006996110607</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1378969872854759</v>
+        <v>0.136445440050892</v>
       </c>
       <c r="W96">
-        <v>0.1265567222664921</v>
+        <v>0.1267698094005291</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8111587487380938</v>
+        <v>0.8026202355934822</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1539191203962972</v>
+        <v>0.2080186005164709</v>
       </c>
       <c r="C97">
-        <v>1.025364818824034</v>
+        <v>0.6552736625615907</v>
       </c>
       <c r="D97">
-        <v>1.766864818824037</v>
+        <v>1.642473662561591</v>
       </c>
       <c r="E97">
-        <v>14.6715</v>
+        <v>14.9172</v>
       </c>
       <c r="F97">
-        <v>23.3415</v>
+        <v>23.5872</v>
       </c>
       <c r="G97">
         <v>22.6</v>
@@ -9354,45 +9354,45 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M97">
-        <v>3.426532200000001</v>
+        <v>4.736309760000001</v>
       </c>
       <c r="N97">
-        <v>-0.6763281183673473</v>
+        <v>-1.986105678367347</v>
       </c>
       <c r="O97">
-        <v>-0.1149757801224491</v>
+        <v>-0.3376379653224491</v>
       </c>
       <c r="P97">
-        <v>-0.5613523382448983</v>
+        <v>-1.648467713044898</v>
       </c>
       <c r="Q97">
-        <v>7.198647661755103</v>
+        <v>6.111532286955102</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6697560293158927</v>
+        <v>0.8569820396492095</v>
       </c>
       <c r="T97">
-        <v>14.41006996110607</v>
+        <v>18.73399629674849</v>
       </c>
       <c r="U97">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.136445440050892</v>
+        <v>0.098712862453817</v>
       </c>
       <c r="W97">
-        <v>0.1267698094005291</v>
+        <v>0.1809784572192736</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.8026202355934822</v>
+        <v>0.5806638967871589</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2080186005164709</v>
+        <v>0.2095686005164709</v>
       </c>
       <c r="C98">
-        <v>0.6552736625615943</v>
+        <v>0.4062673182736489</v>
       </c>
       <c r="D98">
-        <v>1.642473662561591</v>
+        <v>1.639167318273646</v>
       </c>
       <c r="E98">
-        <v>14.9172</v>
+        <v>15.1629</v>
       </c>
       <c r="F98">
-        <v>23.5872</v>
+        <v>23.8329</v>
       </c>
       <c r="G98">
         <v>22.6</v>
@@ -9436,37 +9436,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M98">
-        <v>4.73630976</v>
+        <v>4.78564632</v>
       </c>
       <c r="N98">
-        <v>-1.986105678367347</v>
+        <v>-2.035442238367346</v>
       </c>
       <c r="O98">
-        <v>-0.3376379653224489</v>
+        <v>-0.3460251805224488</v>
       </c>
       <c r="P98">
-        <v>-1.648467713044897</v>
+        <v>-1.689417057844897</v>
       </c>
       <c r="Q98">
-        <v>6.111532286955104</v>
+        <v>6.070582942155103</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8569820396492073</v>
+        <v>1.12737605286561</v>
       </c>
       <c r="T98">
-        <v>18.73399629674844</v>
+        <v>24.97866172899792</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09871286245381702</v>
+        <v>0.0976952040780045</v>
       </c>
       <c r="W98">
-        <v>0.1809784572192736</v>
+        <v>0.1811828030211367</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5806638967871589</v>
+        <v>0.5746776710470851</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2095686005164709</v>
+        <v>0.2111186005164709</v>
       </c>
       <c r="C99">
-        <v>0.4062673182736489</v>
+        <v>0.1572742587655682</v>
       </c>
       <c r="D99">
-        <v>1.639167318273646</v>
+        <v>1.635874258765568</v>
       </c>
       <c r="E99">
-        <v>15.1629</v>
+        <v>15.4086</v>
       </c>
       <c r="F99">
-        <v>23.8329</v>
+        <v>24.0786</v>
       </c>
       <c r="G99">
         <v>22.6</v>
@@ -9518,37 +9518,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M99">
-        <v>4.78564632</v>
+        <v>4.83498288</v>
       </c>
       <c r="N99">
-        <v>-2.035442238367346</v>
+        <v>-2.084778798367346</v>
       </c>
       <c r="O99">
-        <v>-0.3460251805224488</v>
+        <v>-0.3544123957224489</v>
       </c>
       <c r="P99">
-        <v>-1.689417057844897</v>
+        <v>-1.730366402644897</v>
       </c>
       <c r="Q99">
-        <v>6.070582942155103</v>
+        <v>6.029633597355103</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.12737605286561</v>
+        <v>1.668164079298415</v>
       </c>
       <c r="T99">
-        <v>24.97866172899792</v>
+        <v>37.46799259349688</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.0976952040780045</v>
+        <v>0.09669831424047381</v>
       </c>
       <c r="W99">
-        <v>0.1811828030211367</v>
+        <v>0.1813829785005129</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5746776710470851</v>
+        <v>0.5688136131792578</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2111186005164709</v>
+        <v>0.2126686005164709</v>
       </c>
       <c r="C100">
-        <v>0.1572742587655682</v>
+        <v>-0.09170559586880955</v>
       </c>
       <c r="D100">
-        <v>1.635874258765568</v>
+        <v>1.63259440413119</v>
       </c>
       <c r="E100">
-        <v>15.4086</v>
+        <v>15.6543</v>
       </c>
       <c r="F100">
-        <v>24.0786</v>
+        <v>24.3243</v>
       </c>
       <c r="G100">
         <v>22.6</v>
@@ -9600,37 +9600,37 @@
         <v>2.750204081632654</v>
       </c>
       <c r="M100">
-        <v>4.83498288</v>
+        <v>4.884319440000001</v>
       </c>
       <c r="N100">
-        <v>-2.084778798367346</v>
+        <v>-2.134115358367347</v>
       </c>
       <c r="O100">
-        <v>-0.3544123957224489</v>
+        <v>-0.362799610922449</v>
       </c>
       <c r="P100">
-        <v>-1.730366402644897</v>
+        <v>-1.771315747444898</v>
       </c>
       <c r="Q100">
-        <v>6.029633597355103</v>
+        <v>5.988684252555103</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.668164079298415</v>
+        <v>3.29052815859683</v>
       </c>
       <c r="T100">
-        <v>37.46799259349688</v>
+        <v>74.93598518699376</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09669831424047381</v>
+        <v>0.09572156359158014</v>
       </c>
       <c r="W100">
-        <v>0.1813829785005129</v>
+        <v>0.1815791100308107</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9638,91 +9638,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5688136131792578</v>
+        <v>0.563068021126942</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2126686005164709</v>
-      </c>
-      <c r="C101">
-        <v>-0.09170559586880955</v>
-      </c>
-      <c r="D101">
-        <v>1.63259440413119</v>
-      </c>
-      <c r="E101">
-        <v>15.6543</v>
-      </c>
-      <c r="F101">
-        <v>24.3243</v>
-      </c>
-      <c r="G101">
-        <v>22.6</v>
-      </c>
-      <c r="H101">
-        <v>15.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10.51020408163265</v>
-      </c>
-      <c r="K101">
-        <v>7.760000000000001</v>
-      </c>
-      <c r="L101">
-        <v>2.750204081632654</v>
-      </c>
-      <c r="M101">
-        <v>4.884319440000001</v>
-      </c>
-      <c r="N101">
-        <v>-2.134115358367347</v>
-      </c>
-      <c r="O101">
-        <v>-0.362799610922449</v>
-      </c>
-      <c r="P101">
-        <v>-1.771315747444898</v>
-      </c>
-      <c r="Q101">
-        <v>5.988684252555103</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.29052815859683</v>
-      </c>
-      <c r="T101">
-        <v>74.93598518699376</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09572156359158014</v>
-      </c>
-      <c r="W101">
-        <v>0.1815791100308107</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.563068021126942</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
